--- a/docs/詳細設計書/詳細設計書_在庫センター情報画面.xlsx
+++ b/docs/詳細設計書/詳細設計書_在庫センター情報画面.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="19" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="533">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -2116,23 +2116,11 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>現在容量(m3)</t>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>最大容量(m3)</t>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
     <t>最大容量は10文字以内で入力してください。</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>現在容量(m3)</t>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>現在容量は10文字以内で入力してください。</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
@@ -2443,31 +2431,98 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
+    <t xml:space="preserve">　Model </t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  Form</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>Form</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>バリデーション結果</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  バリデーション結果</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>bindingResult</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>/admin/centerInfo/centerNewRegistration</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>2.2.2 ビューを返却</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
     <t>2.2 入力チェック：CenterInfoNewRegistrationValidator</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t xml:space="preserve">　Model </t>
+    <t>在庫センター名＊</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t xml:space="preserve">  Form</t>
+    <t>在庫センター名＊</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>Form</t>
+    <t>郵便番号＊</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>バリデーション結果</t>
+    <t>住所＊</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t xml:space="preserve">  バリデーション結果</t>
+    <t>住所＊</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>bindingResult</t>
+    <t>管理者名＊</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>管理者名＊</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>稼働ステータス＊</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>(空白),null</t>
+    <rPh sb="1" eb="3">
+      <t>クウハク</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>(空白),null</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>(空白),null</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>(空白),null</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>必須項目が未設定です。</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>必須項目が未設定です。</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
@@ -2475,15 +2530,32 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>2.2.2 ビューを返却</t>
+    <t>GET/admin/centerInfo/centerNewRegistration</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>GET/admin/centerNewRegistrationInfo</t>
+    <t>POST/admin/centerInfo/centerNewRegistrationExec</t>
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>POST/admin/centerNewRegistrationInfo</t>
+    <t>最大容量(m3)</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>現在容量は10文字以内で入力してください。</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+◆登録更新削除バリデーションチェック
+バリデーション追加</t>
+    <rPh sb="27" eb="29">
+      <t>ツイカ</t>
+    </rPh>
     <phoneticPr fontId="22"/>
   </si>
 </sst>
@@ -3146,7 +3218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="376">
+  <cellXfs count="378">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3536,15 +3608,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="20" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3590,6 +3656,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4070,6 +4142,18 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4085,17 +4169,173 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4103,172 +4343,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4925,11 +5003,19 @@
         <v>409</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="B8" s="61"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
+    <row r="8" spans="1:5" ht="49.5" x14ac:dyDescent="0.4">
+      <c r="B8" s="61" t="s">
+        <v>531</v>
+      </c>
+      <c r="C8" s="62">
+        <v>45817</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" s="64" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B9" s="61"/>
@@ -7830,7 +7916,7 @@
         <v>60</v>
       </c>
       <c r="G51" s="110" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H51" s="217" t="s">
         <v>358</v>
@@ -18437,7 +18523,7 @@
   <dimension ref="A1:AT223"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="7" width="5.44140625" style="2" customWidth="1"/>
+    <col min="1" max="7" width="7.21875" style="2" customWidth="1"/>
     <col min="8" max="9" width="3.6640625" style="2"/>
     <col min="10" max="11" width="4" style="2" customWidth="1"/>
     <col min="12" max="14" width="5.44140625" style="2" customWidth="1"/>
@@ -18449,135 +18535,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="330" t="s">
+      <c r="A1" s="324" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="331"/>
-      <c r="C1" s="331"/>
-      <c r="D1" s="331"/>
-      <c r="E1" s="331"/>
-      <c r="F1" s="331"/>
-      <c r="G1" s="331"/>
-      <c r="H1" s="331"/>
-      <c r="I1" s="331"/>
-      <c r="J1" s="331"/>
-      <c r="K1" s="331"/>
-      <c r="L1" s="331"/>
-      <c r="M1" s="331"/>
-      <c r="N1" s="332"/>
-      <c r="O1" s="339" t="s">
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="326"/>
+      <c r="O1" s="333" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="339"/>
-      <c r="Q1" s="339"/>
-      <c r="R1" s="339"/>
-      <c r="S1" s="339"/>
-      <c r="T1" s="340" t="s">
+      <c r="P1" s="333"/>
+      <c r="Q1" s="333"/>
+      <c r="R1" s="333"/>
+      <c r="S1" s="333"/>
+      <c r="T1" s="334" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="341"/>
-      <c r="V1" s="341"/>
-      <c r="W1" s="341"/>
-      <c r="X1" s="341"/>
-      <c r="Y1" s="341"/>
-      <c r="Z1" s="341"/>
-      <c r="AA1" s="342"/>
-      <c r="AB1" s="339" t="s">
+      <c r="U1" s="335"/>
+      <c r="V1" s="335"/>
+      <c r="W1" s="335"/>
+      <c r="X1" s="335"/>
+      <c r="Y1" s="335"/>
+      <c r="Z1" s="335"/>
+      <c r="AA1" s="336"/>
+      <c r="AB1" s="333" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="339"/>
-      <c r="AD1" s="339"/>
-      <c r="AE1" s="329" t="s">
+      <c r="AC1" s="333"/>
+      <c r="AD1" s="333"/>
+      <c r="AE1" s="323" t="s">
         <v>6</v>
       </c>
-      <c r="AF1" s="329"/>
-      <c r="AG1" s="329"/>
-      <c r="AH1" s="329"/>
-      <c r="AI1" s="339" t="s">
+      <c r="AF1" s="323"/>
+      <c r="AG1" s="323"/>
+      <c r="AH1" s="323"/>
+      <c r="AI1" s="333" t="s">
         <v>13</v>
       </c>
-      <c r="AJ1" s="339"/>
-      <c r="AK1" s="339"/>
-      <c r="AL1" s="328">
+      <c r="AJ1" s="333"/>
+      <c r="AK1" s="333"/>
+      <c r="AL1" s="322">
         <v>45566</v>
       </c>
     </row>
     <row r="2" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="333"/>
-      <c r="B2" s="334"/>
-      <c r="C2" s="334"/>
-      <c r="D2" s="334"/>
-      <c r="E2" s="334"/>
-      <c r="F2" s="334"/>
-      <c r="G2" s="334"/>
-      <c r="H2" s="334"/>
-      <c r="I2" s="334"/>
-      <c r="J2" s="334"/>
-      <c r="K2" s="334"/>
-      <c r="L2" s="334"/>
-      <c r="M2" s="334"/>
-      <c r="N2" s="335"/>
-      <c r="O2" s="339" t="s">
+      <c r="A2" s="327"/>
+      <c r="B2" s="328"/>
+      <c r="C2" s="328"/>
+      <c r="D2" s="328"/>
+      <c r="E2" s="328"/>
+      <c r="F2" s="328"/>
+      <c r="G2" s="328"/>
+      <c r="H2" s="328"/>
+      <c r="I2" s="328"/>
+      <c r="J2" s="328"/>
+      <c r="K2" s="328"/>
+      <c r="L2" s="328"/>
+      <c r="M2" s="328"/>
+      <c r="N2" s="329"/>
+      <c r="O2" s="333" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="339"/>
-      <c r="Q2" s="339"/>
-      <c r="R2" s="339"/>
-      <c r="S2" s="339"/>
-      <c r="T2" s="340" t="s">
+      <c r="P2" s="333"/>
+      <c r="Q2" s="333"/>
+      <c r="R2" s="333"/>
+      <c r="S2" s="333"/>
+      <c r="T2" s="334" t="s">
         <v>15</v>
       </c>
-      <c r="U2" s="341"/>
-      <c r="V2" s="341"/>
-      <c r="W2" s="341"/>
-      <c r="X2" s="341"/>
-      <c r="Y2" s="341"/>
-      <c r="Z2" s="341"/>
-      <c r="AA2" s="342"/>
-      <c r="AB2" s="339"/>
-      <c r="AC2" s="339"/>
-      <c r="AD2" s="339"/>
-      <c r="AE2" s="329"/>
-      <c r="AF2" s="329"/>
-      <c r="AG2" s="329"/>
-      <c r="AH2" s="329"/>
-      <c r="AI2" s="339"/>
-      <c r="AJ2" s="339"/>
-      <c r="AK2" s="339"/>
-      <c r="AL2" s="329"/>
+      <c r="U2" s="335"/>
+      <c r="V2" s="335"/>
+      <c r="W2" s="335"/>
+      <c r="X2" s="335"/>
+      <c r="Y2" s="335"/>
+      <c r="Z2" s="335"/>
+      <c r="AA2" s="336"/>
+      <c r="AB2" s="333"/>
+      <c r="AC2" s="333"/>
+      <c r="AD2" s="333"/>
+      <c r="AE2" s="323"/>
+      <c r="AF2" s="323"/>
+      <c r="AG2" s="323"/>
+      <c r="AH2" s="323"/>
+      <c r="AI2" s="333"/>
+      <c r="AJ2" s="333"/>
+      <c r="AK2" s="333"/>
+      <c r="AL2" s="323"/>
     </row>
     <row r="3" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="333"/>
-      <c r="B3" s="334"/>
-      <c r="C3" s="334"/>
-      <c r="D3" s="334"/>
-      <c r="E3" s="334"/>
-      <c r="F3" s="334"/>
-      <c r="G3" s="334"/>
-      <c r="H3" s="334"/>
-      <c r="I3" s="334"/>
-      <c r="J3" s="334"/>
-      <c r="K3" s="334"/>
-      <c r="L3" s="334"/>
-      <c r="M3" s="334"/>
-      <c r="N3" s="335"/>
-      <c r="O3" s="339" t="s">
+      <c r="A3" s="327"/>
+      <c r="B3" s="328"/>
+      <c r="C3" s="328"/>
+      <c r="D3" s="328"/>
+      <c r="E3" s="328"/>
+      <c r="F3" s="328"/>
+      <c r="G3" s="328"/>
+      <c r="H3" s="328"/>
+      <c r="I3" s="328"/>
+      <c r="J3" s="328"/>
+      <c r="K3" s="328"/>
+      <c r="L3" s="328"/>
+      <c r="M3" s="328"/>
+      <c r="N3" s="329"/>
+      <c r="O3" s="333" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="339"/>
-      <c r="Q3" s="339"/>
-      <c r="R3" s="339"/>
-      <c r="S3" s="339"/>
-      <c r="T3" s="329" t="s">
+      <c r="P3" s="333"/>
+      <c r="Q3" s="333"/>
+      <c r="R3" s="333"/>
+      <c r="S3" s="333"/>
+      <c r="T3" s="323" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="329"/>
-      <c r="V3" s="329"/>
-      <c r="W3" s="329"/>
-      <c r="X3" s="329"/>
-      <c r="Y3" s="329"/>
-      <c r="Z3" s="329"/>
-      <c r="AA3" s="329"/>
+      <c r="U3" s="323"/>
+      <c r="V3" s="323"/>
+      <c r="W3" s="323"/>
+      <c r="X3" s="323"/>
+      <c r="Y3" s="323"/>
+      <c r="Z3" s="323"/>
+      <c r="AA3" s="323"/>
       <c r="AB3" s="155" t="s">
         <v>18</v>
       </c>
@@ -18599,37 +18685,37 @@
       </c>
     </row>
     <row r="4" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="336"/>
-      <c r="B4" s="337"/>
-      <c r="C4" s="337"/>
-      <c r="D4" s="337"/>
-      <c r="E4" s="337"/>
-      <c r="F4" s="337"/>
-      <c r="G4" s="337"/>
-      <c r="H4" s="337"/>
-      <c r="I4" s="337"/>
-      <c r="J4" s="337"/>
-      <c r="K4" s="337"/>
-      <c r="L4" s="337"/>
-      <c r="M4" s="337"/>
-      <c r="N4" s="338"/>
-      <c r="O4" s="339" t="s">
+      <c r="A4" s="330"/>
+      <c r="B4" s="331"/>
+      <c r="C4" s="331"/>
+      <c r="D4" s="331"/>
+      <c r="E4" s="331"/>
+      <c r="F4" s="331"/>
+      <c r="G4" s="331"/>
+      <c r="H4" s="331"/>
+      <c r="I4" s="331"/>
+      <c r="J4" s="331"/>
+      <c r="K4" s="331"/>
+      <c r="L4" s="331"/>
+      <c r="M4" s="331"/>
+      <c r="N4" s="332"/>
+      <c r="O4" s="333" t="s">
         <v>20</v>
       </c>
-      <c r="P4" s="339"/>
-      <c r="Q4" s="339"/>
-      <c r="R4" s="339"/>
-      <c r="S4" s="339"/>
-      <c r="T4" s="329" t="s">
+      <c r="P4" s="333"/>
+      <c r="Q4" s="333"/>
+      <c r="R4" s="333"/>
+      <c r="S4" s="333"/>
+      <c r="T4" s="323" t="s">
         <v>21</v>
       </c>
-      <c r="U4" s="329"/>
-      <c r="V4" s="329"/>
-      <c r="W4" s="329"/>
-      <c r="X4" s="329"/>
-      <c r="Y4" s="329"/>
-      <c r="Z4" s="329"/>
-      <c r="AA4" s="329"/>
+      <c r="U4" s="323"/>
+      <c r="V4" s="323"/>
+      <c r="W4" s="323"/>
+      <c r="X4" s="323"/>
+      <c r="Y4" s="323"/>
+      <c r="Z4" s="323"/>
+      <c r="AA4" s="323"/>
       <c r="AB4" s="155"/>
       <c r="AC4" s="155"/>
       <c r="AD4" s="155"/>
@@ -18643,28 +18729,28 @@
       <c r="AL4" s="149"/>
     </row>
     <row r="5" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="367" t="s">
+      <c r="A5" s="361" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="315" t="s">
+      <c r="B5" s="361"/>
+      <c r="C5" s="361"/>
+      <c r="D5" s="310" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="316"/>
-      <c r="F5" s="317"/>
-      <c r="G5" s="367" t="s">
+      <c r="E5" s="311"/>
+      <c r="F5" s="312"/>
+      <c r="G5" s="361" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="368" t="s">
+      <c r="H5" s="361"/>
+      <c r="I5" s="361"/>
+      <c r="J5" s="362" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="368"/>
-      <c r="L5" s="368"/>
-      <c r="M5" s="368"/>
-      <c r="N5" s="368"/>
+      <c r="K5" s="362"/>
+      <c r="L5" s="362"/>
+      <c r="M5" s="362"/>
+      <c r="N5" s="362"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
@@ -18691,59 +18777,59 @@
       <c r="AL5" s="7"/>
     </row>
     <row r="6" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="356" t="s">
+      <c r="A6" s="350" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="356"/>
-      <c r="C6" s="356"/>
-      <c r="D6" s="356"/>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
-      <c r="G6" s="356"/>
-      <c r="H6" s="357" t="s">
+      <c r="B6" s="350"/>
+      <c r="C6" s="350"/>
+      <c r="D6" s="350"/>
+      <c r="E6" s="350"/>
+      <c r="F6" s="350"/>
+      <c r="G6" s="350"/>
+      <c r="H6" s="351" t="s">
         <v>131</v>
       </c>
-      <c r="I6" s="358"/>
-      <c r="J6" s="358"/>
-      <c r="K6" s="358"/>
-      <c r="L6" s="358"/>
-      <c r="M6" s="358"/>
-      <c r="N6" s="358"/>
-      <c r="O6" s="358"/>
-      <c r="P6" s="358"/>
-      <c r="Q6" s="358"/>
-      <c r="R6" s="358"/>
-      <c r="S6" s="358"/>
-      <c r="T6" s="358"/>
-      <c r="U6" s="358"/>
-      <c r="V6" s="358"/>
-      <c r="W6" s="358"/>
-      <c r="X6" s="358"/>
-      <c r="Y6" s="358"/>
-      <c r="Z6" s="358"/>
-      <c r="AA6" s="358"/>
-      <c r="AB6" s="358"/>
-      <c r="AC6" s="358"/>
-      <c r="AD6" s="358"/>
-      <c r="AE6" s="359"/>
-      <c r="AF6" s="356" t="s">
+      <c r="I6" s="352"/>
+      <c r="J6" s="352"/>
+      <c r="K6" s="352"/>
+      <c r="L6" s="352"/>
+      <c r="M6" s="352"/>
+      <c r="N6" s="352"/>
+      <c r="O6" s="352"/>
+      <c r="P6" s="352"/>
+      <c r="Q6" s="352"/>
+      <c r="R6" s="352"/>
+      <c r="S6" s="352"/>
+      <c r="T6" s="352"/>
+      <c r="U6" s="352"/>
+      <c r="V6" s="352"/>
+      <c r="W6" s="352"/>
+      <c r="X6" s="352"/>
+      <c r="Y6" s="352"/>
+      <c r="Z6" s="352"/>
+      <c r="AA6" s="352"/>
+      <c r="AB6" s="352"/>
+      <c r="AC6" s="352"/>
+      <c r="AD6" s="352"/>
+      <c r="AE6" s="353"/>
+      <c r="AF6" s="350" t="s">
         <v>132</v>
       </c>
-      <c r="AG6" s="356"/>
-      <c r="AH6" s="356"/>
-      <c r="AI6" s="356"/>
-      <c r="AJ6" s="356"/>
-      <c r="AK6" s="356"/>
-      <c r="AL6" s="356"/>
+      <c r="AG6" s="350"/>
+      <c r="AH6" s="350"/>
+      <c r="AI6" s="350"/>
+      <c r="AJ6" s="350"/>
+      <c r="AK6" s="350"/>
+      <c r="AL6" s="350"/>
     </row>
     <row r="7" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="360"/>
-      <c r="B7" s="361"/>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
-      <c r="E7" s="361"/>
-      <c r="F7" s="361"/>
-      <c r="G7" s="361"/>
+      <c r="A7" s="354"/>
+      <c r="B7" s="355"/>
+      <c r="C7" s="355"/>
+      <c r="D7" s="355"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
+      <c r="G7" s="355"/>
       <c r="H7" s="3"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -18768,24 +18854,24 @@
       <c r="AC7" s="8"/>
       <c r="AD7" s="8"/>
       <c r="AE7" s="10"/>
-      <c r="AF7" s="362"/>
-      <c r="AG7" s="362"/>
-      <c r="AH7" s="362"/>
-      <c r="AI7" s="362"/>
-      <c r="AJ7" s="362"/>
-      <c r="AK7" s="362"/>
-      <c r="AL7" s="363"/>
+      <c r="AF7" s="356"/>
+      <c r="AG7" s="356"/>
+      <c r="AH7" s="356"/>
+      <c r="AI7" s="356"/>
+      <c r="AJ7" s="356"/>
+      <c r="AK7" s="356"/>
+      <c r="AL7" s="357"/>
     </row>
     <row r="8" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="354" t="s">
+      <c r="A8" s="348" t="s">
         <v>284</v>
       </c>
-      <c r="B8" s="355"/>
-      <c r="C8" s="355"/>
-      <c r="D8" s="355"/>
-      <c r="E8" s="355"/>
-      <c r="F8" s="355"/>
-      <c r="G8" s="355"/>
+      <c r="B8" s="349"/>
+      <c r="C8" s="349"/>
+      <c r="D8" s="349"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
+      <c r="G8" s="349"/>
       <c r="H8" s="104"/>
       <c r="I8" s="82" t="s">
         <v>418</v>
@@ -18798,47 +18884,47 @@
       <c r="O8" s="82"/>
       <c r="P8" s="82"/>
       <c r="AE8" s="107"/>
-      <c r="AF8" s="350"/>
-      <c r="AG8" s="350"/>
-      <c r="AH8" s="350"/>
-      <c r="AI8" s="350"/>
-      <c r="AJ8" s="350"/>
-      <c r="AK8" s="350"/>
-      <c r="AL8" s="351"/>
+      <c r="AF8" s="344"/>
+      <c r="AG8" s="344"/>
+      <c r="AH8" s="344"/>
+      <c r="AI8" s="344"/>
+      <c r="AJ8" s="344"/>
+      <c r="AK8" s="344"/>
+      <c r="AL8" s="345"/>
     </row>
     <row r="9" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="354" t="s">
+      <c r="A9" s="348" t="s">
         <v>290</v>
       </c>
-      <c r="B9" s="355"/>
-      <c r="C9" s="355"/>
-      <c r="D9" s="355"/>
-      <c r="E9" s="355"/>
-      <c r="F9" s="355"/>
-      <c r="G9" s="355"/>
+      <c r="B9" s="349"/>
+      <c r="C9" s="349"/>
+      <c r="D9" s="349"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
+      <c r="G9" s="349"/>
       <c r="H9" s="104"/>
       <c r="J9" s="1" t="s">
         <v>133</v>
       </c>
       <c r="AE9" s="107"/>
-      <c r="AF9" s="350"/>
-      <c r="AG9" s="350"/>
-      <c r="AH9" s="350"/>
-      <c r="AI9" s="350"/>
-      <c r="AJ9" s="350"/>
-      <c r="AK9" s="350"/>
-      <c r="AL9" s="351"/>
+      <c r="AF9" s="344"/>
+      <c r="AG9" s="344"/>
+      <c r="AH9" s="344"/>
+      <c r="AI9" s="344"/>
+      <c r="AJ9" s="344"/>
+      <c r="AK9" s="344"/>
+      <c r="AL9" s="345"/>
     </row>
     <row r="10" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="354" t="s">
+      <c r="A10" s="348" t="s">
         <v>134</v>
       </c>
-      <c r="B10" s="355"/>
-      <c r="C10" s="355"/>
-      <c r="D10" s="355"/>
-      <c r="E10" s="355"/>
-      <c r="F10" s="355"/>
-      <c r="G10" s="355"/>
+      <c r="B10" s="349"/>
+      <c r="C10" s="349"/>
+      <c r="D10" s="349"/>
+      <c r="E10" s="349"/>
+      <c r="F10" s="349"/>
+      <c r="G10" s="349"/>
       <c r="H10" s="104"/>
       <c r="K10" s="1" t="s">
         <v>135</v>
@@ -18874,87 +18960,87 @@
       <c r="AL11" s="108"/>
     </row>
     <row r="12" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="354"/>
-      <c r="B12" s="355"/>
-      <c r="C12" s="355"/>
-      <c r="D12" s="355"/>
-      <c r="E12" s="355"/>
-      <c r="F12" s="355"/>
-      <c r="G12" s="355"/>
+      <c r="A12" s="348"/>
+      <c r="B12" s="349"/>
+      <c r="C12" s="349"/>
+      <c r="D12" s="349"/>
+      <c r="E12" s="349"/>
+      <c r="F12" s="349"/>
+      <c r="G12" s="349"/>
       <c r="H12" s="104"/>
       <c r="AE12" s="107"/>
-      <c r="AF12" s="350"/>
-      <c r="AG12" s="350"/>
-      <c r="AH12" s="350"/>
-      <c r="AI12" s="350"/>
-      <c r="AJ12" s="350"/>
-      <c r="AK12" s="350"/>
-      <c r="AL12" s="351"/>
+      <c r="AF12" s="344"/>
+      <c r="AG12" s="344"/>
+      <c r="AH12" s="344"/>
+      <c r="AI12" s="344"/>
+      <c r="AJ12" s="344"/>
+      <c r="AK12" s="344"/>
+      <c r="AL12" s="345"/>
     </row>
     <row r="13" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="354"/>
-      <c r="B13" s="355"/>
-      <c r="C13" s="355"/>
-      <c r="D13" s="355"/>
-      <c r="E13" s="355"/>
-      <c r="F13" s="355"/>
-      <c r="G13" s="355"/>
+      <c r="A13" s="348"/>
+      <c r="B13" s="349"/>
+      <c r="C13" s="349"/>
+      <c r="D13" s="349"/>
+      <c r="E13" s="349"/>
+      <c r="F13" s="349"/>
+      <c r="G13" s="349"/>
       <c r="H13" s="104"/>
       <c r="J13" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AE13" s="107"/>
-      <c r="AF13" s="355" t="s">
+      <c r="AF13" s="349" t="s">
         <v>138</v>
       </c>
-      <c r="AG13" s="355"/>
-      <c r="AH13" s="355"/>
-      <c r="AI13" s="355"/>
-      <c r="AJ13" s="355"/>
-      <c r="AK13" s="355"/>
-      <c r="AL13" s="364"/>
+      <c r="AG13" s="349"/>
+      <c r="AH13" s="349"/>
+      <c r="AI13" s="349"/>
+      <c r="AJ13" s="349"/>
+      <c r="AK13" s="349"/>
+      <c r="AL13" s="358"/>
     </row>
     <row r="14" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="354"/>
-      <c r="B14" s="355"/>
-      <c r="C14" s="355"/>
-      <c r="D14" s="355"/>
-      <c r="E14" s="355"/>
-      <c r="F14" s="355"/>
-      <c r="G14" s="355"/>
+      <c r="A14" s="348"/>
+      <c r="B14" s="349"/>
+      <c r="C14" s="349"/>
+      <c r="D14" s="349"/>
+      <c r="E14" s="349"/>
+      <c r="F14" s="349"/>
+      <c r="G14" s="349"/>
       <c r="H14" s="104"/>
       <c r="K14" s="1" t="s">
         <v>139</v>
       </c>
       <c r="AE14" s="107"/>
-      <c r="AF14" s="350"/>
-      <c r="AG14" s="350"/>
-      <c r="AH14" s="350"/>
-      <c r="AI14" s="350"/>
-      <c r="AJ14" s="350"/>
-      <c r="AK14" s="350"/>
-      <c r="AL14" s="351"/>
+      <c r="AF14" s="344"/>
+      <c r="AG14" s="344"/>
+      <c r="AH14" s="344"/>
+      <c r="AI14" s="344"/>
+      <c r="AJ14" s="344"/>
+      <c r="AK14" s="344"/>
+      <c r="AL14" s="345"/>
     </row>
     <row r="15" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="354"/>
-      <c r="B15" s="355"/>
-      <c r="C15" s="355"/>
-      <c r="D15" s="355"/>
-      <c r="E15" s="355"/>
-      <c r="F15" s="355"/>
-      <c r="G15" s="355"/>
+      <c r="A15" s="348"/>
+      <c r="B15" s="349"/>
+      <c r="C15" s="349"/>
+      <c r="D15" s="349"/>
+      <c r="E15" s="349"/>
+      <c r="F15" s="349"/>
+      <c r="G15" s="349"/>
       <c r="H15" s="104"/>
       <c r="K15" s="1" t="s">
         <v>140</v>
       </c>
       <c r="AE15" s="107"/>
-      <c r="AF15" s="350"/>
-      <c r="AG15" s="350"/>
-      <c r="AH15" s="350"/>
-      <c r="AI15" s="350"/>
-      <c r="AJ15" s="350"/>
-      <c r="AK15" s="350"/>
-      <c r="AL15" s="351"/>
+      <c r="AF15" s="344"/>
+      <c r="AG15" s="344"/>
+      <c r="AH15" s="344"/>
+      <c r="AI15" s="344"/>
+      <c r="AJ15" s="344"/>
+      <c r="AK15" s="344"/>
+      <c r="AL15" s="345"/>
     </row>
     <row r="16" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="103"/>
@@ -18996,15 +19082,15 @@
       <c r="AL17" s="108"/>
     </row>
     <row r="18" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="355" t="s">
+      <c r="A18" s="349" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="355"/>
-      <c r="C18" s="355"/>
-      <c r="D18" s="355"/>
-      <c r="E18" s="355"/>
-      <c r="F18" s="355"/>
-      <c r="G18" s="364"/>
+      <c r="B18" s="349"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
+      <c r="G18" s="358"/>
       <c r="H18" s="104"/>
       <c r="J18" s="1" t="s">
         <v>141</v>
@@ -19037,25 +19123,25 @@
       <c r="AL19" s="108"/>
     </row>
     <row r="20" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="354"/>
-      <c r="B20" s="355"/>
-      <c r="C20" s="355"/>
-      <c r="D20" s="355"/>
-      <c r="E20" s="355"/>
-      <c r="F20" s="355"/>
-      <c r="G20" s="355"/>
+      <c r="A20" s="348"/>
+      <c r="B20" s="349"/>
+      <c r="C20" s="349"/>
+      <c r="D20" s="349"/>
+      <c r="E20" s="349"/>
+      <c r="F20" s="349"/>
+      <c r="G20" s="349"/>
       <c r="H20" s="104"/>
       <c r="J20" s="1" t="s">
         <v>142</v>
       </c>
       <c r="AE20" s="107"/>
-      <c r="AF20" s="350"/>
-      <c r="AG20" s="350"/>
-      <c r="AH20" s="350"/>
-      <c r="AI20" s="350"/>
-      <c r="AJ20" s="350"/>
-      <c r="AK20" s="350"/>
-      <c r="AL20" s="351"/>
+      <c r="AF20" s="344"/>
+      <c r="AG20" s="344"/>
+      <c r="AH20" s="344"/>
+      <c r="AI20" s="344"/>
+      <c r="AJ20" s="344"/>
+      <c r="AK20" s="344"/>
+      <c r="AL20" s="345"/>
     </row>
     <row r="21" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="103"/>
@@ -19159,15 +19245,15 @@
       <c r="AL25" s="108"/>
     </row>
     <row r="26" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="354" t="s">
+      <c r="A26" s="348" t="s">
         <v>422</v>
       </c>
-      <c r="B26" s="355"/>
-      <c r="C26" s="355"/>
-      <c r="D26" s="355"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
-      <c r="G26" s="355"/>
+      <c r="B26" s="349"/>
+      <c r="C26" s="349"/>
+      <c r="D26" s="349"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="349"/>
+      <c r="G26" s="349"/>
       <c r="H26" s="4"/>
       <c r="I26" s="16" t="s">
         <v>419</v>
@@ -19194,36 +19280,36 @@
       <c r="AC26" s="5"/>
       <c r="AD26" s="5"/>
       <c r="AE26" s="11"/>
-      <c r="AF26" s="365"/>
-      <c r="AG26" s="365"/>
-      <c r="AH26" s="365"/>
-      <c r="AI26" s="365"/>
-      <c r="AJ26" s="365"/>
-      <c r="AK26" s="365"/>
-      <c r="AL26" s="366"/>
+      <c r="AF26" s="359"/>
+      <c r="AG26" s="359"/>
+      <c r="AH26" s="359"/>
+      <c r="AI26" s="359"/>
+      <c r="AJ26" s="359"/>
+      <c r="AK26" s="359"/>
+      <c r="AL26" s="360"/>
     </row>
     <row r="27" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="354" t="s">
+      <c r="A27" s="348" t="s">
         <v>146</v>
       </c>
-      <c r="B27" s="355"/>
-      <c r="C27" s="355"/>
-      <c r="D27" s="355"/>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
-      <c r="G27" s="355"/>
+      <c r="B27" s="349"/>
+      <c r="C27" s="349"/>
+      <c r="D27" s="349"/>
+      <c r="E27" s="349"/>
+      <c r="F27" s="349"/>
+      <c r="G27" s="349"/>
       <c r="H27" s="104"/>
       <c r="J27" s="1" t="s">
         <v>147</v>
       </c>
       <c r="AE27" s="107"/>
-      <c r="AF27" s="350"/>
-      <c r="AG27" s="350"/>
-      <c r="AH27" s="350"/>
-      <c r="AI27" s="350"/>
-      <c r="AJ27" s="350"/>
-      <c r="AK27" s="350"/>
-      <c r="AL27" s="351"/>
+      <c r="AF27" s="344"/>
+      <c r="AG27" s="344"/>
+      <c r="AH27" s="344"/>
+      <c r="AI27" s="344"/>
+      <c r="AJ27" s="344"/>
+      <c r="AK27" s="344"/>
+      <c r="AL27" s="345"/>
     </row>
     <row r="28" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="103"/>
@@ -19274,7 +19360,7 @@
     <row r="30" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="105"/>
       <c r="B30" s="68" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C30" s="106"/>
       <c r="D30" s="106"/>
@@ -19512,32 +19598,32 @@
       <c r="H36" s="4"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
-      <c r="K36" s="339" t="s">
+      <c r="K36" s="333" t="s">
         <v>152</v>
       </c>
-      <c r="L36" s="339"/>
-      <c r="M36" s="339"/>
-      <c r="N36" s="339"/>
-      <c r="O36" s="339"/>
-      <c r="P36" s="343" t="s">
+      <c r="L36" s="333"/>
+      <c r="M36" s="333"/>
+      <c r="N36" s="333"/>
+      <c r="O36" s="333"/>
+      <c r="P36" s="337" t="s">
         <v>153</v>
       </c>
-      <c r="Q36" s="344"/>
-      <c r="R36" s="344"/>
-      <c r="S36" s="344"/>
-      <c r="T36" s="344"/>
-      <c r="U36" s="344"/>
-      <c r="V36" s="344"/>
-      <c r="W36" s="344"/>
-      <c r="X36" s="344"/>
-      <c r="Y36" s="344"/>
-      <c r="Z36" s="345"/>
-      <c r="AA36" s="339" t="s">
+      <c r="Q36" s="338"/>
+      <c r="R36" s="338"/>
+      <c r="S36" s="338"/>
+      <c r="T36" s="338"/>
+      <c r="U36" s="338"/>
+      <c r="V36" s="338"/>
+      <c r="W36" s="338"/>
+      <c r="X36" s="338"/>
+      <c r="Y36" s="338"/>
+      <c r="Z36" s="339"/>
+      <c r="AA36" s="333" t="s">
         <v>127</v>
       </c>
-      <c r="AB36" s="339"/>
-      <c r="AC36" s="339"/>
-      <c r="AD36" s="339"/>
+      <c r="AB36" s="333"/>
+      <c r="AC36" s="333"/>
+      <c r="AD36" s="333"/>
       <c r="AE36" s="11"/>
       <c r="AF36" s="5"/>
       <c r="AG36" s="5"/>
@@ -19558,32 +19644,32 @@
       <c r="H37" s="4"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
-      <c r="K37" s="353">
+      <c r="K37" s="347">
         <v>1.23456789011121E+29</v>
       </c>
-      <c r="L37" s="346"/>
-      <c r="M37" s="346"/>
-      <c r="N37" s="346"/>
-      <c r="O37" s="346"/>
-      <c r="P37" s="347" t="s">
+      <c r="L37" s="340"/>
+      <c r="M37" s="340"/>
+      <c r="N37" s="340"/>
+      <c r="O37" s="340"/>
+      <c r="P37" s="341" t="s">
         <v>206</v>
       </c>
-      <c r="Q37" s="348"/>
-      <c r="R37" s="348"/>
-      <c r="S37" s="348"/>
-      <c r="T37" s="348"/>
-      <c r="U37" s="348"/>
-      <c r="V37" s="348"/>
-      <c r="W37" s="348"/>
-      <c r="X37" s="348"/>
-      <c r="Y37" s="348"/>
-      <c r="Z37" s="349"/>
-      <c r="AA37" s="329" t="s">
+      <c r="Q37" s="342"/>
+      <c r="R37" s="342"/>
+      <c r="S37" s="342"/>
+      <c r="T37" s="342"/>
+      <c r="U37" s="342"/>
+      <c r="V37" s="342"/>
+      <c r="W37" s="342"/>
+      <c r="X37" s="342"/>
+      <c r="Y37" s="342"/>
+      <c r="Z37" s="343"/>
+      <c r="AA37" s="323" t="s">
         <v>387</v>
       </c>
-      <c r="AB37" s="329"/>
-      <c r="AC37" s="329"/>
-      <c r="AD37" s="329"/>
+      <c r="AB37" s="323"/>
+      <c r="AC37" s="323"/>
+      <c r="AD37" s="323"/>
       <c r="AE37" s="11"/>
       <c r="AF37" s="5"/>
       <c r="AG37" s="5"/>
@@ -19604,32 +19690,32 @@
       <c r="H38" s="4"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
-      <c r="K38" s="346" t="s">
+      <c r="K38" s="340" t="s">
         <v>128</v>
       </c>
-      <c r="L38" s="346"/>
-      <c r="M38" s="346"/>
-      <c r="N38" s="346"/>
-      <c r="O38" s="346"/>
-      <c r="P38" s="347" t="s">
+      <c r="L38" s="340"/>
+      <c r="M38" s="340"/>
+      <c r="N38" s="340"/>
+      <c r="O38" s="340"/>
+      <c r="P38" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q38" s="348"/>
-      <c r="R38" s="348"/>
-      <c r="S38" s="348"/>
-      <c r="T38" s="348"/>
-      <c r="U38" s="348"/>
-      <c r="V38" s="348"/>
-      <c r="W38" s="348"/>
-      <c r="X38" s="348"/>
-      <c r="Y38" s="348"/>
-      <c r="Z38" s="349"/>
-      <c r="AA38" s="329" t="s">
+      <c r="Q38" s="342"/>
+      <c r="R38" s="342"/>
+      <c r="S38" s="342"/>
+      <c r="T38" s="342"/>
+      <c r="U38" s="342"/>
+      <c r="V38" s="342"/>
+      <c r="W38" s="342"/>
+      <c r="X38" s="342"/>
+      <c r="Y38" s="342"/>
+      <c r="Z38" s="343"/>
+      <c r="AA38" s="323" t="s">
         <v>154</v>
       </c>
-      <c r="AB38" s="329"/>
-      <c r="AC38" s="329"/>
-      <c r="AD38" s="329"/>
+      <c r="AB38" s="323"/>
+      <c r="AC38" s="323"/>
+      <c r="AD38" s="323"/>
       <c r="AE38" s="11"/>
       <c r="AF38" s="5"/>
       <c r="AG38" s="5"/>
@@ -19650,32 +19736,32 @@
       <c r="H39" s="4"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
-      <c r="K39" s="346" t="s">
+      <c r="K39" s="340" t="s">
         <v>186</v>
       </c>
-      <c r="L39" s="346"/>
-      <c r="M39" s="346"/>
-      <c r="N39" s="346"/>
-      <c r="O39" s="346"/>
-      <c r="P39" s="347" t="s">
+      <c r="L39" s="340"/>
+      <c r="M39" s="340"/>
+      <c r="N39" s="340"/>
+      <c r="O39" s="340"/>
+      <c r="P39" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q39" s="348"/>
-      <c r="R39" s="348"/>
-      <c r="S39" s="348"/>
-      <c r="T39" s="348"/>
-      <c r="U39" s="348"/>
-      <c r="V39" s="348"/>
-      <c r="W39" s="348"/>
-      <c r="X39" s="348"/>
-      <c r="Y39" s="348"/>
-      <c r="Z39" s="349"/>
-      <c r="AA39" s="329" t="s">
+      <c r="Q39" s="342"/>
+      <c r="R39" s="342"/>
+      <c r="S39" s="342"/>
+      <c r="T39" s="342"/>
+      <c r="U39" s="342"/>
+      <c r="V39" s="342"/>
+      <c r="W39" s="342"/>
+      <c r="X39" s="342"/>
+      <c r="Y39" s="342"/>
+      <c r="Z39" s="343"/>
+      <c r="AA39" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB39" s="329"/>
-      <c r="AC39" s="329"/>
-      <c r="AD39" s="329"/>
+      <c r="AB39" s="323"/>
+      <c r="AC39" s="323"/>
+      <c r="AD39" s="323"/>
       <c r="AE39" s="11"/>
       <c r="AF39" s="5"/>
       <c r="AG39" s="5"/>
@@ -19696,32 +19782,32 @@
       <c r="H40" s="4"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
-      <c r="K40" s="346" t="s">
+      <c r="K40" s="340" t="s">
         <v>185</v>
       </c>
-      <c r="L40" s="346"/>
-      <c r="M40" s="346"/>
-      <c r="N40" s="346"/>
-      <c r="O40" s="346"/>
-      <c r="P40" s="347" t="s">
+      <c r="L40" s="340"/>
+      <c r="M40" s="340"/>
+      <c r="N40" s="340"/>
+      <c r="O40" s="340"/>
+      <c r="P40" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q40" s="348"/>
-      <c r="R40" s="348"/>
-      <c r="S40" s="348"/>
-      <c r="T40" s="348"/>
-      <c r="U40" s="348"/>
-      <c r="V40" s="348"/>
-      <c r="W40" s="348"/>
-      <c r="X40" s="348"/>
-      <c r="Y40" s="348"/>
-      <c r="Z40" s="349"/>
-      <c r="AA40" s="329" t="s">
+      <c r="Q40" s="342"/>
+      <c r="R40" s="342"/>
+      <c r="S40" s="342"/>
+      <c r="T40" s="342"/>
+      <c r="U40" s="342"/>
+      <c r="V40" s="342"/>
+      <c r="W40" s="342"/>
+      <c r="X40" s="342"/>
+      <c r="Y40" s="342"/>
+      <c r="Z40" s="343"/>
+      <c r="AA40" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB40" s="329"/>
-      <c r="AC40" s="329"/>
-      <c r="AD40" s="329"/>
+      <c r="AB40" s="323"/>
+      <c r="AC40" s="323"/>
+      <c r="AD40" s="323"/>
       <c r="AE40" s="11"/>
       <c r="AF40" s="5"/>
       <c r="AG40" s="5"/>
@@ -19742,32 +19828,32 @@
       <c r="H41" s="4"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
-      <c r="K41" s="346" t="s">
+      <c r="K41" s="340" t="s">
         <v>156</v>
       </c>
-      <c r="L41" s="346"/>
-      <c r="M41" s="346"/>
-      <c r="N41" s="346"/>
-      <c r="O41" s="346"/>
-      <c r="P41" s="347" t="s">
+      <c r="L41" s="340"/>
+      <c r="M41" s="340"/>
+      <c r="N41" s="340"/>
+      <c r="O41" s="340"/>
+      <c r="P41" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q41" s="348"/>
-      <c r="R41" s="348"/>
-      <c r="S41" s="348"/>
-      <c r="T41" s="348"/>
-      <c r="U41" s="348"/>
-      <c r="V41" s="348"/>
-      <c r="W41" s="348"/>
-      <c r="X41" s="348"/>
-      <c r="Y41" s="348"/>
-      <c r="Z41" s="349"/>
-      <c r="AA41" s="329" t="s">
+      <c r="Q41" s="342"/>
+      <c r="R41" s="342"/>
+      <c r="S41" s="342"/>
+      <c r="T41" s="342"/>
+      <c r="U41" s="342"/>
+      <c r="V41" s="342"/>
+      <c r="W41" s="342"/>
+      <c r="X41" s="342"/>
+      <c r="Y41" s="342"/>
+      <c r="Z41" s="343"/>
+      <c r="AA41" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB41" s="329"/>
-      <c r="AC41" s="329"/>
-      <c r="AD41" s="329"/>
+      <c r="AB41" s="323"/>
+      <c r="AC41" s="323"/>
+      <c r="AD41" s="323"/>
       <c r="AE41" s="11"/>
       <c r="AF41" s="5"/>
       <c r="AG41" s="5"/>
@@ -19788,32 +19874,32 @@
       <c r="H42" s="4"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
-      <c r="K42" s="346" t="s">
+      <c r="K42" s="340" t="s">
         <v>157</v>
       </c>
-      <c r="L42" s="346"/>
-      <c r="M42" s="346"/>
-      <c r="N42" s="346"/>
-      <c r="O42" s="346"/>
-      <c r="P42" s="347" t="s">
+      <c r="L42" s="340"/>
+      <c r="M42" s="340"/>
+      <c r="N42" s="340"/>
+      <c r="O42" s="340"/>
+      <c r="P42" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q42" s="348"/>
-      <c r="R42" s="348"/>
-      <c r="S42" s="348"/>
-      <c r="T42" s="348"/>
-      <c r="U42" s="348"/>
-      <c r="V42" s="348"/>
-      <c r="W42" s="348"/>
-      <c r="X42" s="348"/>
-      <c r="Y42" s="348"/>
-      <c r="Z42" s="349"/>
-      <c r="AA42" s="329" t="s">
+      <c r="Q42" s="342"/>
+      <c r="R42" s="342"/>
+      <c r="S42" s="342"/>
+      <c r="T42" s="342"/>
+      <c r="U42" s="342"/>
+      <c r="V42" s="342"/>
+      <c r="W42" s="342"/>
+      <c r="X42" s="342"/>
+      <c r="Y42" s="342"/>
+      <c r="Z42" s="343"/>
+      <c r="AA42" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB42" s="329"/>
-      <c r="AC42" s="329"/>
-      <c r="AD42" s="329"/>
+      <c r="AB42" s="323"/>
+      <c r="AC42" s="323"/>
+      <c r="AD42" s="323"/>
       <c r="AE42" s="11"/>
       <c r="AF42" s="5"/>
       <c r="AG42" s="5"/>
@@ -19834,32 +19920,32 @@
       <c r="H43" s="4"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="352" t="s">
+      <c r="K43" s="346" t="s">
         <v>158</v>
       </c>
-      <c r="L43" s="346"/>
-      <c r="M43" s="346"/>
-      <c r="N43" s="346"/>
-      <c r="O43" s="346"/>
-      <c r="P43" s="347" t="s">
+      <c r="L43" s="340"/>
+      <c r="M43" s="340"/>
+      <c r="N43" s="340"/>
+      <c r="O43" s="340"/>
+      <c r="P43" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q43" s="348"/>
-      <c r="R43" s="348"/>
-      <c r="S43" s="348"/>
-      <c r="T43" s="348"/>
-      <c r="U43" s="348"/>
-      <c r="V43" s="348"/>
-      <c r="W43" s="348"/>
-      <c r="X43" s="348"/>
-      <c r="Y43" s="348"/>
-      <c r="Z43" s="349"/>
-      <c r="AA43" s="329" t="s">
+      <c r="Q43" s="342"/>
+      <c r="R43" s="342"/>
+      <c r="S43" s="342"/>
+      <c r="T43" s="342"/>
+      <c r="U43" s="342"/>
+      <c r="V43" s="342"/>
+      <c r="W43" s="342"/>
+      <c r="X43" s="342"/>
+      <c r="Y43" s="342"/>
+      <c r="Z43" s="343"/>
+      <c r="AA43" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB43" s="329"/>
-      <c r="AC43" s="329"/>
-      <c r="AD43" s="329"/>
+      <c r="AB43" s="323"/>
+      <c r="AC43" s="323"/>
+      <c r="AD43" s="323"/>
       <c r="AE43" s="11"/>
       <c r="AF43" s="69"/>
       <c r="AG43" s="69"/>
@@ -19880,32 +19966,32 @@
       <c r="H44" s="4"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
-      <c r="K44" s="352" t="s">
+      <c r="K44" s="346" t="s">
         <v>124</v>
       </c>
-      <c r="L44" s="346"/>
-      <c r="M44" s="346"/>
-      <c r="N44" s="346"/>
-      <c r="O44" s="346"/>
-      <c r="P44" s="347" t="s">
+      <c r="L44" s="340"/>
+      <c r="M44" s="340"/>
+      <c r="N44" s="340"/>
+      <c r="O44" s="340"/>
+      <c r="P44" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q44" s="348"/>
-      <c r="R44" s="348"/>
-      <c r="S44" s="348"/>
-      <c r="T44" s="348"/>
-      <c r="U44" s="348"/>
-      <c r="V44" s="348"/>
-      <c r="W44" s="348"/>
-      <c r="X44" s="348"/>
-      <c r="Y44" s="348"/>
-      <c r="Z44" s="349"/>
-      <c r="AA44" s="329" t="s">
+      <c r="Q44" s="342"/>
+      <c r="R44" s="342"/>
+      <c r="S44" s="342"/>
+      <c r="T44" s="342"/>
+      <c r="U44" s="342"/>
+      <c r="V44" s="342"/>
+      <c r="W44" s="342"/>
+      <c r="X44" s="342"/>
+      <c r="Y44" s="342"/>
+      <c r="Z44" s="343"/>
+      <c r="AA44" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB44" s="329"/>
-      <c r="AC44" s="329"/>
-      <c r="AD44" s="329"/>
+      <c r="AB44" s="323"/>
+      <c r="AC44" s="323"/>
+      <c r="AD44" s="323"/>
       <c r="AE44" s="11"/>
       <c r="AF44" s="69"/>
       <c r="AG44" s="69"/>
@@ -19926,32 +20012,32 @@
       <c r="H45" s="4"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="352" t="s">
+      <c r="K45" s="346" t="s">
         <v>159</v>
       </c>
-      <c r="L45" s="346"/>
-      <c r="M45" s="346"/>
-      <c r="N45" s="346"/>
-      <c r="O45" s="346"/>
-      <c r="P45" s="347" t="s">
+      <c r="L45" s="340"/>
+      <c r="M45" s="340"/>
+      <c r="N45" s="340"/>
+      <c r="O45" s="340"/>
+      <c r="P45" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q45" s="348"/>
-      <c r="R45" s="348"/>
-      <c r="S45" s="348"/>
-      <c r="T45" s="348"/>
-      <c r="U45" s="348"/>
-      <c r="V45" s="348"/>
-      <c r="W45" s="348"/>
-      <c r="X45" s="348"/>
-      <c r="Y45" s="348"/>
-      <c r="Z45" s="349"/>
-      <c r="AA45" s="329" t="s">
+      <c r="Q45" s="342"/>
+      <c r="R45" s="342"/>
+      <c r="S45" s="342"/>
+      <c r="T45" s="342"/>
+      <c r="U45" s="342"/>
+      <c r="V45" s="342"/>
+      <c r="W45" s="342"/>
+      <c r="X45" s="342"/>
+      <c r="Y45" s="342"/>
+      <c r="Z45" s="343"/>
+      <c r="AA45" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB45" s="329"/>
-      <c r="AC45" s="329"/>
-      <c r="AD45" s="329"/>
+      <c r="AB45" s="323"/>
+      <c r="AC45" s="323"/>
+      <c r="AD45" s="323"/>
       <c r="AE45" s="11"/>
       <c r="AF45" s="69"/>
       <c r="AG45" s="69"/>
@@ -19972,32 +20058,32 @@
       <c r="H46" s="4"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
-      <c r="K46" s="352" t="s">
+      <c r="K46" s="346" t="s">
         <v>160</v>
       </c>
-      <c r="L46" s="346"/>
-      <c r="M46" s="346"/>
-      <c r="N46" s="346"/>
-      <c r="O46" s="346"/>
-      <c r="P46" s="347" t="s">
+      <c r="L46" s="340"/>
+      <c r="M46" s="340"/>
+      <c r="N46" s="340"/>
+      <c r="O46" s="340"/>
+      <c r="P46" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q46" s="348"/>
-      <c r="R46" s="348"/>
-      <c r="S46" s="348"/>
-      <c r="T46" s="348"/>
-      <c r="U46" s="348"/>
-      <c r="V46" s="348"/>
-      <c r="W46" s="348"/>
-      <c r="X46" s="348"/>
-      <c r="Y46" s="348"/>
-      <c r="Z46" s="349"/>
-      <c r="AA46" s="329" t="s">
+      <c r="Q46" s="342"/>
+      <c r="R46" s="342"/>
+      <c r="S46" s="342"/>
+      <c r="T46" s="342"/>
+      <c r="U46" s="342"/>
+      <c r="V46" s="342"/>
+      <c r="W46" s="342"/>
+      <c r="X46" s="342"/>
+      <c r="Y46" s="342"/>
+      <c r="Z46" s="343"/>
+      <c r="AA46" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB46" s="329"/>
-      <c r="AC46" s="329"/>
-      <c r="AD46" s="329"/>
+      <c r="AB46" s="323"/>
+      <c r="AC46" s="323"/>
+      <c r="AD46" s="323"/>
       <c r="AE46" s="11"/>
       <c r="AF46" s="69"/>
       <c r="AG46" s="69"/>
@@ -20018,32 +20104,32 @@
       <c r="H47" s="4"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
-      <c r="K47" s="352" t="s">
+      <c r="K47" s="346" t="s">
         <v>161</v>
       </c>
-      <c r="L47" s="346"/>
-      <c r="M47" s="346"/>
-      <c r="N47" s="346"/>
-      <c r="O47" s="346"/>
-      <c r="P47" s="347" t="s">
+      <c r="L47" s="340"/>
+      <c r="M47" s="340"/>
+      <c r="N47" s="340"/>
+      <c r="O47" s="340"/>
+      <c r="P47" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q47" s="348"/>
-      <c r="R47" s="348"/>
-      <c r="S47" s="348"/>
-      <c r="T47" s="348"/>
-      <c r="U47" s="348"/>
-      <c r="V47" s="348"/>
-      <c r="W47" s="348"/>
-      <c r="X47" s="348"/>
-      <c r="Y47" s="348"/>
-      <c r="Z47" s="349"/>
-      <c r="AA47" s="329" t="s">
+      <c r="Q47" s="342"/>
+      <c r="R47" s="342"/>
+      <c r="S47" s="342"/>
+      <c r="T47" s="342"/>
+      <c r="U47" s="342"/>
+      <c r="V47" s="342"/>
+      <c r="W47" s="342"/>
+      <c r="X47" s="342"/>
+      <c r="Y47" s="342"/>
+      <c r="Z47" s="343"/>
+      <c r="AA47" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB47" s="329"/>
-      <c r="AC47" s="329"/>
-      <c r="AD47" s="329"/>
+      <c r="AB47" s="323"/>
+      <c r="AC47" s="323"/>
+      <c r="AD47" s="323"/>
       <c r="AE47" s="11"/>
       <c r="AF47" s="69"/>
       <c r="AG47" s="69"/>
@@ -20064,32 +20150,32 @@
       <c r="H48" s="4"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
-      <c r="K48" s="352" t="s">
+      <c r="K48" s="346" t="s">
         <v>162</v>
       </c>
-      <c r="L48" s="346"/>
-      <c r="M48" s="346"/>
-      <c r="N48" s="346"/>
-      <c r="O48" s="346"/>
-      <c r="P48" s="347" t="s">
+      <c r="L48" s="340"/>
+      <c r="M48" s="340"/>
+      <c r="N48" s="340"/>
+      <c r="O48" s="340"/>
+      <c r="P48" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q48" s="348"/>
-      <c r="R48" s="348"/>
-      <c r="S48" s="348"/>
-      <c r="T48" s="348"/>
-      <c r="U48" s="348"/>
-      <c r="V48" s="348"/>
-      <c r="W48" s="348"/>
-      <c r="X48" s="348"/>
-      <c r="Y48" s="348"/>
-      <c r="Z48" s="349"/>
-      <c r="AA48" s="329" t="s">
+      <c r="Q48" s="342"/>
+      <c r="R48" s="342"/>
+      <c r="S48" s="342"/>
+      <c r="T48" s="342"/>
+      <c r="U48" s="342"/>
+      <c r="V48" s="342"/>
+      <c r="W48" s="342"/>
+      <c r="X48" s="342"/>
+      <c r="Y48" s="342"/>
+      <c r="Z48" s="343"/>
+      <c r="AA48" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB48" s="329"/>
-      <c r="AC48" s="329"/>
-      <c r="AD48" s="329"/>
+      <c r="AB48" s="323"/>
+      <c r="AC48" s="323"/>
+      <c r="AD48" s="323"/>
       <c r="AE48" s="11"/>
       <c r="AF48" s="69"/>
       <c r="AG48" s="69"/>
@@ -20192,32 +20278,32 @@
       <c r="H51" s="4"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
-      <c r="K51" s="339" t="s">
+      <c r="K51" s="333" t="s">
         <v>152</v>
       </c>
-      <c r="L51" s="339"/>
-      <c r="M51" s="339"/>
-      <c r="N51" s="339"/>
-      <c r="O51" s="339"/>
-      <c r="P51" s="343" t="s">
+      <c r="L51" s="333"/>
+      <c r="M51" s="333"/>
+      <c r="N51" s="333"/>
+      <c r="O51" s="333"/>
+      <c r="P51" s="337" t="s">
         <v>153</v>
       </c>
-      <c r="Q51" s="344"/>
-      <c r="R51" s="344"/>
-      <c r="S51" s="344"/>
-      <c r="T51" s="344"/>
-      <c r="U51" s="344"/>
-      <c r="V51" s="344"/>
-      <c r="W51" s="344"/>
-      <c r="X51" s="344"/>
-      <c r="Y51" s="344"/>
-      <c r="Z51" s="345"/>
-      <c r="AA51" s="339" t="s">
+      <c r="Q51" s="338"/>
+      <c r="R51" s="338"/>
+      <c r="S51" s="338"/>
+      <c r="T51" s="338"/>
+      <c r="U51" s="338"/>
+      <c r="V51" s="338"/>
+      <c r="W51" s="338"/>
+      <c r="X51" s="338"/>
+      <c r="Y51" s="338"/>
+      <c r="Z51" s="339"/>
+      <c r="AA51" s="333" t="s">
         <v>127</v>
       </c>
-      <c r="AB51" s="339"/>
-      <c r="AC51" s="339"/>
-      <c r="AD51" s="339"/>
+      <c r="AB51" s="333"/>
+      <c r="AC51" s="333"/>
+      <c r="AD51" s="333"/>
       <c r="AE51" s="11"/>
       <c r="AF51" s="5"/>
       <c r="AG51" s="5"/>
@@ -20238,32 +20324,32 @@
       <c r="H52" s="4"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
-      <c r="K52" s="346" t="s">
+      <c r="K52" s="340" t="s">
         <v>164</v>
       </c>
-      <c r="L52" s="346"/>
-      <c r="M52" s="346"/>
-      <c r="N52" s="346"/>
-      <c r="O52" s="346"/>
-      <c r="P52" s="347" t="s">
+      <c r="L52" s="340"/>
+      <c r="M52" s="340"/>
+      <c r="N52" s="340"/>
+      <c r="O52" s="340"/>
+      <c r="P52" s="341" t="s">
         <v>125</v>
       </c>
-      <c r="Q52" s="348"/>
-      <c r="R52" s="348"/>
-      <c r="S52" s="348"/>
-      <c r="T52" s="348"/>
-      <c r="U52" s="348"/>
-      <c r="V52" s="348"/>
-      <c r="W52" s="348"/>
-      <c r="X52" s="348"/>
-      <c r="Y52" s="348"/>
-      <c r="Z52" s="349"/>
-      <c r="AA52" s="329" t="s">
+      <c r="Q52" s="342"/>
+      <c r="R52" s="342"/>
+      <c r="S52" s="342"/>
+      <c r="T52" s="342"/>
+      <c r="U52" s="342"/>
+      <c r="V52" s="342"/>
+      <c r="W52" s="342"/>
+      <c r="X52" s="342"/>
+      <c r="Y52" s="342"/>
+      <c r="Z52" s="343"/>
+      <c r="AA52" s="323" t="s">
         <v>155</v>
       </c>
-      <c r="AB52" s="329"/>
-      <c r="AC52" s="329"/>
-      <c r="AD52" s="329"/>
+      <c r="AB52" s="323"/>
+      <c r="AC52" s="323"/>
+      <c r="AD52" s="323"/>
       <c r="AE52" s="11"/>
       <c r="AF52" s="5"/>
       <c r="AG52" s="5"/>
@@ -20408,32 +20494,32 @@
       <c r="H56" s="4"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
-      <c r="K56" s="339" t="s">
+      <c r="K56" s="333" t="s">
         <v>152</v>
       </c>
-      <c r="L56" s="339"/>
-      <c r="M56" s="339"/>
-      <c r="N56" s="339"/>
-      <c r="O56" s="339"/>
-      <c r="P56" s="343" t="s">
+      <c r="L56" s="333"/>
+      <c r="M56" s="333"/>
+      <c r="N56" s="333"/>
+      <c r="O56" s="333"/>
+      <c r="P56" s="337" t="s">
         <v>153</v>
       </c>
-      <c r="Q56" s="344"/>
-      <c r="R56" s="344"/>
-      <c r="S56" s="344"/>
-      <c r="T56" s="344"/>
-      <c r="U56" s="344"/>
-      <c r="V56" s="344"/>
-      <c r="W56" s="344"/>
-      <c r="X56" s="344"/>
-      <c r="Y56" s="344"/>
-      <c r="Z56" s="345"/>
-      <c r="AA56" s="339" t="s">
+      <c r="Q56" s="338"/>
+      <c r="R56" s="338"/>
+      <c r="S56" s="338"/>
+      <c r="T56" s="338"/>
+      <c r="U56" s="338"/>
+      <c r="V56" s="338"/>
+      <c r="W56" s="338"/>
+      <c r="X56" s="338"/>
+      <c r="Y56" s="338"/>
+      <c r="Z56" s="339"/>
+      <c r="AA56" s="333" t="s">
         <v>127</v>
       </c>
-      <c r="AB56" s="339"/>
-      <c r="AC56" s="339"/>
-      <c r="AD56" s="339"/>
+      <c r="AB56" s="333"/>
+      <c r="AC56" s="333"/>
+      <c r="AD56" s="333"/>
       <c r="AE56" s="11"/>
       <c r="AF56" s="69"/>
       <c r="AG56" s="69"/>
@@ -20454,32 +20540,32 @@
       <c r="H57" s="4"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
-      <c r="K57" s="353" t="s">
+      <c r="K57" s="347" t="s">
         <v>197</v>
       </c>
-      <c r="L57" s="346"/>
-      <c r="M57" s="346"/>
-      <c r="N57" s="346"/>
-      <c r="O57" s="346"/>
-      <c r="P57" s="347" t="s">
+      <c r="L57" s="340"/>
+      <c r="M57" s="340"/>
+      <c r="N57" s="340"/>
+      <c r="O57" s="340"/>
+      <c r="P57" s="341" t="s">
         <v>195</v>
       </c>
-      <c r="Q57" s="348"/>
-      <c r="R57" s="348"/>
-      <c r="S57" s="348"/>
-      <c r="T57" s="348"/>
-      <c r="U57" s="348"/>
-      <c r="V57" s="348"/>
-      <c r="W57" s="348"/>
-      <c r="X57" s="348"/>
-      <c r="Y57" s="348"/>
-      <c r="Z57" s="349"/>
-      <c r="AA57" s="329" t="s">
+      <c r="Q57" s="342"/>
+      <c r="R57" s="342"/>
+      <c r="S57" s="342"/>
+      <c r="T57" s="342"/>
+      <c r="U57" s="342"/>
+      <c r="V57" s="342"/>
+      <c r="W57" s="342"/>
+      <c r="X57" s="342"/>
+      <c r="Y57" s="342"/>
+      <c r="Z57" s="343"/>
+      <c r="AA57" s="323" t="s">
         <v>196</v>
       </c>
-      <c r="AB57" s="329"/>
-      <c r="AC57" s="329"/>
-      <c r="AD57" s="329"/>
+      <c r="AB57" s="323"/>
+      <c r="AC57" s="323"/>
+      <c r="AD57" s="323"/>
       <c r="AE57" s="11"/>
       <c r="AF57" s="5"/>
       <c r="AG57" s="1"/>
@@ -20500,30 +20586,30 @@
       <c r="H58" s="4"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
-      <c r="K58" s="353"/>
-      <c r="L58" s="346"/>
-      <c r="M58" s="346"/>
-      <c r="N58" s="346"/>
-      <c r="O58" s="346"/>
-      <c r="P58" s="347" t="s">
+      <c r="K58" s="347"/>
+      <c r="L58" s="340"/>
+      <c r="M58" s="340"/>
+      <c r="N58" s="340"/>
+      <c r="O58" s="340"/>
+      <c r="P58" s="341" t="s">
         <v>207</v>
       </c>
-      <c r="Q58" s="348"/>
-      <c r="R58" s="348"/>
-      <c r="S58" s="348"/>
-      <c r="T58" s="348"/>
-      <c r="U58" s="348"/>
-      <c r="V58" s="348"/>
-      <c r="W58" s="348"/>
-      <c r="X58" s="348"/>
-      <c r="Y58" s="348"/>
-      <c r="Z58" s="349"/>
-      <c r="AA58" s="329" t="s">
+      <c r="Q58" s="342"/>
+      <c r="R58" s="342"/>
+      <c r="S58" s="342"/>
+      <c r="T58" s="342"/>
+      <c r="U58" s="342"/>
+      <c r="V58" s="342"/>
+      <c r="W58" s="342"/>
+      <c r="X58" s="342"/>
+      <c r="Y58" s="342"/>
+      <c r="Z58" s="343"/>
+      <c r="AA58" s="323" t="s">
         <v>388</v>
       </c>
-      <c r="AB58" s="329"/>
-      <c r="AC58" s="329"/>
-      <c r="AD58" s="329"/>
+      <c r="AB58" s="323"/>
+      <c r="AC58" s="323"/>
+      <c r="AD58" s="323"/>
       <c r="AE58" s="11"/>
       <c r="AF58" s="5"/>
       <c r="AG58" s="1"/>
@@ -20880,7 +20966,7 @@
       <c r="H67" s="4"/>
       <c r="I67" s="5"/>
       <c r="J67" s="16" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
@@ -21801,36 +21887,36 @@
       <c r="H89" s="152"/>
       <c r="I89" s="152"/>
       <c r="J89" s="307" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="K89" s="307"/>
       <c r="L89" s="307"/>
       <c r="M89" s="307"/>
       <c r="N89" s="307"/>
-      <c r="O89" s="136"/>
-      <c r="P89" s="136"/>
-      <c r="Q89" s="136"/>
-      <c r="R89" s="136"/>
-      <c r="S89" s="136"/>
-      <c r="T89" s="136"/>
-      <c r="U89" s="136"/>
-      <c r="V89" s="136"/>
-      <c r="W89" s="136"/>
-      <c r="X89" s="136"/>
-      <c r="Y89" s="136"/>
-      <c r="Z89" s="136"/>
-      <c r="AA89" s="136"/>
-      <c r="AB89" s="136"/>
-      <c r="AC89" s="136"/>
-      <c r="AD89" s="136"/>
-      <c r="AE89" s="136"/>
-      <c r="AF89" s="136"/>
-      <c r="AG89" s="136"/>
-      <c r="AH89" s="136"/>
-      <c r="AI89" s="136"/>
-      <c r="AJ89" s="136"/>
-      <c r="AK89" s="136"/>
-      <c r="AL89" s="137"/>
+      <c r="O89" s="134"/>
+      <c r="P89" s="134"/>
+      <c r="Q89" s="134"/>
+      <c r="R89" s="134"/>
+      <c r="S89" s="134"/>
+      <c r="T89" s="134"/>
+      <c r="U89" s="134"/>
+      <c r="V89" s="134"/>
+      <c r="W89" s="134"/>
+      <c r="X89" s="134"/>
+      <c r="Y89" s="134"/>
+      <c r="Z89" s="134"/>
+      <c r="AA89" s="134"/>
+      <c r="AB89" s="134"/>
+      <c r="AC89" s="134"/>
+      <c r="AD89" s="134"/>
+      <c r="AE89" s="134"/>
+      <c r="AF89" s="134"/>
+      <c r="AG89" s="134"/>
+      <c r="AH89" s="134"/>
+      <c r="AI89" s="134"/>
+      <c r="AJ89" s="134"/>
+      <c r="AK89" s="134"/>
+      <c r="AL89" s="135"/>
     </row>
     <row r="90" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="152" t="s">
@@ -21880,7 +21966,7 @@
     </row>
     <row r="91" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="320" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="B91" s="321"/>
       <c r="C91" s="321"/>
@@ -21890,7 +21976,7 @@
       <c r="G91" s="321"/>
       <c r="H91" s="15"/>
       <c r="I91" s="128" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J91" s="127"/>
       <c r="K91" s="16"/>
@@ -21914,24 +22000,24 @@
       <c r="AC91" s="16"/>
       <c r="AD91" s="16"/>
       <c r="AE91" s="21"/>
-      <c r="AF91" s="322"/>
-      <c r="AG91" s="322"/>
-      <c r="AH91" s="322"/>
-      <c r="AI91" s="322"/>
-      <c r="AJ91" s="322"/>
-      <c r="AK91" s="322"/>
-      <c r="AL91" s="323"/>
+      <c r="AF91" s="366"/>
+      <c r="AG91" s="366"/>
+      <c r="AH91" s="366"/>
+      <c r="AI91" s="366"/>
+      <c r="AJ91" s="366"/>
+      <c r="AK91" s="366"/>
+      <c r="AL91" s="367"/>
     </row>
     <row r="92" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="324" t="s">
+      <c r="A92" s="363" t="s">
         <v>290</v>
       </c>
-      <c r="B92" s="325"/>
-      <c r="C92" s="325"/>
-      <c r="D92" s="325"/>
-      <c r="E92" s="325"/>
-      <c r="F92" s="325"/>
-      <c r="G92" s="325"/>
+      <c r="B92" s="364"/>
+      <c r="C92" s="364"/>
+      <c r="D92" s="364"/>
+      <c r="E92" s="364"/>
+      <c r="F92" s="364"/>
+      <c r="G92" s="364"/>
       <c r="H92" s="81"/>
       <c r="I92" s="82"/>
       <c r="J92" s="82" t="s">
@@ -21958,24 +22044,24 @@
       <c r="AC92" s="82"/>
       <c r="AD92" s="82"/>
       <c r="AE92" s="87"/>
-      <c r="AF92" s="326"/>
-      <c r="AG92" s="326"/>
-      <c r="AH92" s="326"/>
-      <c r="AI92" s="326"/>
-      <c r="AJ92" s="326"/>
-      <c r="AK92" s="326"/>
-      <c r="AL92" s="327"/>
+      <c r="AF92" s="318"/>
+      <c r="AG92" s="318"/>
+      <c r="AH92" s="318"/>
+      <c r="AI92" s="318"/>
+      <c r="AJ92" s="318"/>
+      <c r="AK92" s="318"/>
+      <c r="AL92" s="319"/>
     </row>
     <row r="93" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="324" t="s">
+      <c r="A93" s="363" t="s">
         <v>134</v>
       </c>
-      <c r="B93" s="325"/>
-      <c r="C93" s="325"/>
-      <c r="D93" s="325"/>
-      <c r="E93" s="325"/>
-      <c r="F93" s="325"/>
-      <c r="G93" s="325"/>
+      <c r="B93" s="364"/>
+      <c r="C93" s="364"/>
+      <c r="D93" s="364"/>
+      <c r="E93" s="364"/>
+      <c r="F93" s="364"/>
+      <c r="G93" s="364"/>
       <c r="H93" s="81"/>
       <c r="I93" s="82"/>
       <c r="J93" s="82"/>
@@ -22008,21 +22094,21 @@
       <c r="AI93" s="96"/>
       <c r="AJ93" s="96"/>
       <c r="AK93" s="96"/>
-      <c r="AL93" s="138"/>
+      <c r="AL93" s="136"/>
     </row>
     <row r="94" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="139"/>
-      <c r="B94" s="140"/>
-      <c r="C94" s="140"/>
-      <c r="D94" s="140"/>
-      <c r="E94" s="140"/>
-      <c r="F94" s="140"/>
-      <c r="G94" s="140"/>
+      <c r="A94" s="137"/>
+      <c r="B94" s="138"/>
+      <c r="C94" s="138"/>
+      <c r="D94" s="138"/>
+      <c r="E94" s="138"/>
+      <c r="F94" s="138"/>
+      <c r="G94" s="138"/>
       <c r="H94" s="81"/>
       <c r="I94" s="82"/>
       <c r="J94" s="82"/>
       <c r="K94" s="82" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L94" s="82"/>
       <c r="M94" s="82"/>
@@ -22050,16 +22136,16 @@
       <c r="AI94" s="96"/>
       <c r="AJ94" s="96"/>
       <c r="AK94" s="96"/>
-      <c r="AL94" s="138"/>
+      <c r="AL94" s="136"/>
     </row>
     <row r="95" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="324"/>
-      <c r="B95" s="325"/>
-      <c r="C95" s="325"/>
-      <c r="D95" s="325"/>
-      <c r="E95" s="325"/>
-      <c r="F95" s="325"/>
-      <c r="G95" s="325"/>
+      <c r="A95" s="363"/>
+      <c r="B95" s="364"/>
+      <c r="C95" s="364"/>
+      <c r="D95" s="364"/>
+      <c r="E95" s="364"/>
+      <c r="F95" s="364"/>
+      <c r="G95" s="364"/>
       <c r="H95" s="81"/>
       <c r="I95" s="82"/>
       <c r="J95" s="82"/>
@@ -22084,26 +22170,26 @@
       <c r="AC95" s="82"/>
       <c r="AD95" s="82"/>
       <c r="AE95" s="87"/>
-      <c r="AF95" s="326"/>
-      <c r="AG95" s="326"/>
-      <c r="AH95" s="326"/>
-      <c r="AI95" s="326"/>
-      <c r="AJ95" s="326"/>
-      <c r="AK95" s="326"/>
-      <c r="AL95" s="327"/>
+      <c r="AF95" s="318"/>
+      <c r="AG95" s="318"/>
+      <c r="AH95" s="318"/>
+      <c r="AI95" s="318"/>
+      <c r="AJ95" s="318"/>
+      <c r="AK95" s="318"/>
+      <c r="AL95" s="319"/>
     </row>
     <row r="96" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="324"/>
-      <c r="B96" s="325"/>
-      <c r="C96" s="325"/>
-      <c r="D96" s="325"/>
-      <c r="E96" s="325"/>
-      <c r="F96" s="325"/>
-      <c r="G96" s="325"/>
+      <c r="A96" s="363"/>
+      <c r="B96" s="364"/>
+      <c r="C96" s="364"/>
+      <c r="D96" s="364"/>
+      <c r="E96" s="364"/>
+      <c r="F96" s="364"/>
+      <c r="G96" s="364"/>
       <c r="H96" s="81"/>
       <c r="I96" s="82"/>
       <c r="J96" s="82" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K96" s="82"/>
       <c r="L96" s="82"/>
@@ -22126,22 +22212,22 @@
       <c r="AC96" s="82"/>
       <c r="AD96" s="82"/>
       <c r="AE96" s="87"/>
-      <c r="AF96" s="325"/>
-      <c r="AG96" s="325"/>
-      <c r="AH96" s="325"/>
-      <c r="AI96" s="325"/>
-      <c r="AJ96" s="325"/>
-      <c r="AK96" s="325"/>
-      <c r="AL96" s="369"/>
+      <c r="AF96" s="364"/>
+      <c r="AG96" s="364"/>
+      <c r="AH96" s="364"/>
+      <c r="AI96" s="364"/>
+      <c r="AJ96" s="364"/>
+      <c r="AK96" s="364"/>
+      <c r="AL96" s="365"/>
     </row>
     <row r="97" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="324"/>
-      <c r="B97" s="325"/>
-      <c r="C97" s="325"/>
-      <c r="D97" s="325"/>
-      <c r="E97" s="325"/>
-      <c r="F97" s="325"/>
-      <c r="G97" s="325"/>
+      <c r="A97" s="363"/>
+      <c r="B97" s="364"/>
+      <c r="C97" s="364"/>
+      <c r="D97" s="364"/>
+      <c r="E97" s="364"/>
+      <c r="F97" s="364"/>
+      <c r="G97" s="364"/>
       <c r="H97" s="81"/>
       <c r="I97" s="82"/>
       <c r="J97" s="82"/>
@@ -22168,27 +22254,27 @@
       <c r="AC97" s="82"/>
       <c r="AD97" s="82"/>
       <c r="AE97" s="87"/>
-      <c r="AF97" s="326"/>
-      <c r="AG97" s="326"/>
-      <c r="AH97" s="326"/>
-      <c r="AI97" s="326"/>
-      <c r="AJ97" s="326"/>
-      <c r="AK97" s="326"/>
-      <c r="AL97" s="327"/>
+      <c r="AF97" s="318"/>
+      <c r="AG97" s="318"/>
+      <c r="AH97" s="318"/>
+      <c r="AI97" s="318"/>
+      <c r="AJ97" s="318"/>
+      <c r="AK97" s="318"/>
+      <c r="AL97" s="319"/>
     </row>
     <row r="98" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="324"/>
-      <c r="B98" s="325"/>
-      <c r="C98" s="325"/>
-      <c r="D98" s="325"/>
-      <c r="E98" s="325"/>
-      <c r="F98" s="325"/>
-      <c r="G98" s="325"/>
+      <c r="A98" s="363"/>
+      <c r="B98" s="364"/>
+      <c r="C98" s="364"/>
+      <c r="D98" s="364"/>
+      <c r="E98" s="364"/>
+      <c r="F98" s="364"/>
+      <c r="G98" s="364"/>
       <c r="H98" s="81"/>
       <c r="I98" s="82"/>
       <c r="J98" s="82"/>
       <c r="K98" s="82" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L98" s="82"/>
       <c r="M98" s="82"/>
@@ -22210,22 +22296,22 @@
       <c r="AC98" s="82"/>
       <c r="AD98" s="82"/>
       <c r="AE98" s="87"/>
-      <c r="AF98" s="326"/>
-      <c r="AG98" s="326"/>
-      <c r="AH98" s="326"/>
-      <c r="AI98" s="326"/>
-      <c r="AJ98" s="326"/>
-      <c r="AK98" s="326"/>
-      <c r="AL98" s="327"/>
+      <c r="AF98" s="318"/>
+      <c r="AG98" s="318"/>
+      <c r="AH98" s="318"/>
+      <c r="AI98" s="318"/>
+      <c r="AJ98" s="318"/>
+      <c r="AK98" s="318"/>
+      <c r="AL98" s="319"/>
     </row>
     <row r="99" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="139"/>
-      <c r="B99" s="140"/>
-      <c r="C99" s="140"/>
-      <c r="D99" s="140"/>
-      <c r="E99" s="140"/>
-      <c r="F99" s="140"/>
-      <c r="G99" s="140"/>
+      <c r="A99" s="137"/>
+      <c r="B99" s="138"/>
+      <c r="C99" s="138"/>
+      <c r="D99" s="138"/>
+      <c r="E99" s="138"/>
+      <c r="F99" s="138"/>
+      <c r="G99" s="138"/>
       <c r="H99" s="81"/>
       <c r="I99" s="82"/>
       <c r="J99" s="12"/>
@@ -22259,17 +22345,17 @@
       <c r="AL99" s="12"/>
     </row>
     <row r="100" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="325"/>
-      <c r="B100" s="325"/>
-      <c r="C100" s="325"/>
-      <c r="D100" s="325"/>
-      <c r="E100" s="325"/>
-      <c r="F100" s="325"/>
-      <c r="G100" s="369"/>
+      <c r="A100" s="364"/>
+      <c r="B100" s="364"/>
+      <c r="C100" s="364"/>
+      <c r="D100" s="364"/>
+      <c r="E100" s="364"/>
+      <c r="F100" s="364"/>
+      <c r="G100" s="365"/>
       <c r="H100" s="81"/>
       <c r="I100" s="82"/>
       <c r="J100" s="129" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K100" s="129"/>
       <c r="L100" s="129"/>
@@ -22292,23 +22378,23 @@
       <c r="AC100" s="82"/>
       <c r="AD100" s="82"/>
       <c r="AE100" s="87"/>
-      <c r="AF100" s="145" t="s">
-        <v>513</v>
+      <c r="AF100" s="143" t="s">
+        <v>526</v>
       </c>
       <c r="AG100" s="96"/>
       <c r="AH100" s="96"/>
       <c r="AI100" s="96"/>
       <c r="AJ100" s="96"/>
       <c r="AK100" s="96"/>
-      <c r="AL100" s="138"/>
+      <c r="AL100" s="136"/>
     </row>
     <row r="101" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B101" s="140"/>
-      <c r="C101" s="140"/>
-      <c r="D101" s="140"/>
-      <c r="E101" s="140"/>
-      <c r="F101" s="140"/>
-      <c r="G101" s="140"/>
+      <c r="B101" s="138"/>
+      <c r="C101" s="138"/>
+      <c r="D101" s="138"/>
+      <c r="E101" s="138"/>
+      <c r="F101" s="138"/>
+      <c r="G101" s="138"/>
       <c r="H101" s="81"/>
       <c r="I101" s="82"/>
       <c r="J101" s="82"/>
@@ -22339,7 +22425,7 @@
       <c r="AI101" s="96"/>
       <c r="AJ101" s="96"/>
       <c r="AK101" s="96"/>
-      <c r="AL101" s="138"/>
+      <c r="AL101" s="136"/>
     </row>
     <row r="102" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="320" t="s">
@@ -22353,7 +22439,7 @@
       <c r="G102" s="321"/>
       <c r="H102" s="15"/>
       <c r="I102" s="128" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J102" s="127"/>
       <c r="K102" s="16"/>
@@ -22377,17 +22463,17 @@
       <c r="AC102" s="82"/>
       <c r="AD102" s="82"/>
       <c r="AE102" s="87"/>
-      <c r="AF102" s="140"/>
+      <c r="AF102" s="138"/>
       <c r="AG102" s="96"/>
       <c r="AH102" s="96"/>
       <c r="AI102" s="96"/>
       <c r="AJ102" s="96"/>
       <c r="AK102" s="96"/>
-      <c r="AL102" s="138"/>
+      <c r="AL102" s="136"/>
     </row>
     <row r="103" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="320" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B103" s="321"/>
       <c r="C103" s="321"/>
@@ -22398,7 +22484,7 @@
       <c r="H103" s="15"/>
       <c r="I103" s="82"/>
       <c r="J103" s="82" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K103" s="82"/>
       <c r="L103" s="82"/>
@@ -22421,24 +22507,24 @@
       <c r="AC103" s="82"/>
       <c r="AD103" s="82"/>
       <c r="AE103" s="87"/>
-      <c r="AF103" s="140"/>
+      <c r="AF103" s="138"/>
       <c r="AG103" s="96"/>
       <c r="AH103" s="96"/>
       <c r="AI103" s="96"/>
       <c r="AJ103" s="96"/>
       <c r="AK103" s="96"/>
-      <c r="AL103" s="138"/>
+      <c r="AL103" s="136"/>
     </row>
     <row r="104" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="145" t="s">
-        <v>508</v>
-      </c>
-      <c r="B104" s="145"/>
-      <c r="C104" s="145"/>
-      <c r="D104" s="145"/>
-      <c r="E104" s="145"/>
-      <c r="F104" s="145"/>
-      <c r="G104" s="145"/>
+      <c r="A104" s="143" t="s">
+        <v>504</v>
+      </c>
+      <c r="B104" s="143"/>
+      <c r="C104" s="143"/>
+      <c r="D104" s="143"/>
+      <c r="E104" s="143"/>
+      <c r="F104" s="143"/>
+      <c r="G104" s="143"/>
       <c r="H104" s="15"/>
       <c r="I104" s="82"/>
       <c r="J104" s="82"/>
@@ -22465,29 +22551,29 @@
       <c r="AC104" s="82"/>
       <c r="AD104" s="82"/>
       <c r="AE104" s="87"/>
-      <c r="AF104" s="140"/>
+      <c r="AF104" s="138"/>
       <c r="AG104" s="96"/>
       <c r="AH104" s="96"/>
       <c r="AI104" s="96"/>
       <c r="AJ104" s="96"/>
       <c r="AK104" s="96"/>
-      <c r="AL104" s="138"/>
+      <c r="AL104" s="136"/>
     </row>
     <row r="105" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="128" t="s">
-        <v>511</v>
-      </c>
-      <c r="B105" s="145"/>
-      <c r="C105" s="145"/>
-      <c r="D105" s="145"/>
-      <c r="E105" s="145"/>
-      <c r="F105" s="145"/>
-      <c r="G105" s="145"/>
+        <v>507</v>
+      </c>
+      <c r="B105" s="143"/>
+      <c r="C105" s="143"/>
+      <c r="D105" s="143"/>
+      <c r="E105" s="143"/>
+      <c r="F105" s="143"/>
+      <c r="G105" s="143"/>
       <c r="H105" s="15"/>
       <c r="I105" s="82"/>
       <c r="J105" s="82"/>
       <c r="K105" s="82" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="L105" s="82"/>
       <c r="M105" s="82"/>
@@ -22509,17 +22595,17 @@
       <c r="AC105" s="82"/>
       <c r="AD105" s="82"/>
       <c r="AE105" s="87"/>
-      <c r="AF105" s="140"/>
+      <c r="AF105" s="138"/>
       <c r="AG105" s="96"/>
       <c r="AH105" s="96"/>
       <c r="AI105" s="96"/>
       <c r="AJ105" s="96"/>
       <c r="AK105" s="96"/>
-      <c r="AL105" s="138"/>
+      <c r="AL105" s="136"/>
     </row>
     <row r="106" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="145" t="s">
-        <v>474</v>
+      <c r="A106" s="143" t="s">
+        <v>471</v>
       </c>
       <c r="H106" s="81"/>
       <c r="I106" s="82"/>
@@ -22545,28 +22631,28 @@
       <c r="AC106" s="82"/>
       <c r="AD106" s="82"/>
       <c r="AE106" s="87"/>
-      <c r="AF106" s="326"/>
-      <c r="AG106" s="326"/>
-      <c r="AH106" s="326"/>
-      <c r="AI106" s="326"/>
-      <c r="AJ106" s="326"/>
-      <c r="AK106" s="326"/>
-      <c r="AL106" s="327"/>
+      <c r="AF106" s="318"/>
+      <c r="AG106" s="318"/>
+      <c r="AH106" s="318"/>
+      <c r="AI106" s="318"/>
+      <c r="AJ106" s="318"/>
+      <c r="AK106" s="318"/>
+      <c r="AL106" s="319"/>
     </row>
     <row r="107" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="320" t="s">
-        <v>516</v>
-      </c>
-      <c r="B107" s="321"/>
-      <c r="C107" s="321"/>
-      <c r="D107" s="321"/>
-      <c r="E107" s="321"/>
-      <c r="F107" s="321"/>
-      <c r="G107" s="321"/>
+        <v>528</v>
+      </c>
+      <c r="B107" s="376"/>
+      <c r="C107" s="376"/>
+      <c r="D107" s="376"/>
+      <c r="E107" s="376"/>
+      <c r="F107" s="376"/>
+      <c r="G107" s="377"/>
       <c r="H107" s="81"/>
       <c r="I107" s="127"/>
       <c r="J107" s="128" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K107" s="16"/>
       <c r="L107" s="16"/>
@@ -22595,23 +22681,23 @@
       <c r="AI107" s="96"/>
       <c r="AJ107" s="96"/>
       <c r="AK107" s="96"/>
-      <c r="AL107" s="138"/>
+      <c r="AL107" s="136"/>
     </row>
     <row r="108" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="324" t="s">
+      <c r="A108" s="363" t="s">
         <v>146</v>
       </c>
-      <c r="B108" s="325"/>
-      <c r="C108" s="325"/>
-      <c r="D108" s="325"/>
-      <c r="E108" s="325"/>
-      <c r="F108" s="325"/>
-      <c r="G108" s="325"/>
+      <c r="B108" s="364"/>
+      <c r="C108" s="364"/>
+      <c r="D108" s="364"/>
+      <c r="E108" s="364"/>
+      <c r="F108" s="364"/>
+      <c r="G108" s="364"/>
       <c r="H108" s="81"/>
       <c r="I108" s="16"/>
       <c r="J108" s="16"/>
       <c r="K108" s="128" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="L108" s="128"/>
       <c r="M108" s="128"/>
@@ -22639,23 +22725,23 @@
       <c r="AI108" s="96"/>
       <c r="AJ108" s="96"/>
       <c r="AK108" s="96"/>
-      <c r="AL108" s="138"/>
+      <c r="AL108" s="136"/>
     </row>
     <row r="109" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="139"/>
-      <c r="B109" s="140" t="s">
+      <c r="A109" s="137"/>
+      <c r="B109" s="138" t="s">
         <v>148</v>
       </c>
-      <c r="C109" s="140"/>
-      <c r="D109" s="140"/>
-      <c r="E109" s="140"/>
-      <c r="F109" s="140"/>
-      <c r="G109" s="140"/>
+      <c r="C109" s="138"/>
+      <c r="D109" s="138"/>
+      <c r="E109" s="138"/>
+      <c r="F109" s="138"/>
+      <c r="G109" s="138"/>
       <c r="H109" s="81"/>
       <c r="I109" s="12"/>
       <c r="J109" s="12"/>
-      <c r="K109" s="135" t="s">
-        <v>454</v>
+      <c r="K109" s="133" t="s">
+        <v>451</v>
       </c>
       <c r="L109" s="16"/>
       <c r="M109" s="16"/>
@@ -22677,27 +22763,27 @@
       <c r="AC109" s="82"/>
       <c r="AD109" s="16"/>
       <c r="AE109" s="87"/>
-      <c r="AG109" s="146"/>
-      <c r="AH109" s="146"/>
-      <c r="AI109" s="146"/>
-      <c r="AJ109" s="146"/>
-      <c r="AK109" s="146"/>
-      <c r="AL109" s="147"/>
+      <c r="AG109" s="144"/>
+      <c r="AH109" s="144"/>
+      <c r="AI109" s="144"/>
+      <c r="AJ109" s="144"/>
+      <c r="AK109" s="144"/>
+      <c r="AL109" s="145"/>
     </row>
     <row r="110" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="139"/>
-      <c r="B110" s="145" t="s">
-        <v>509</v>
-      </c>
-      <c r="C110" s="140"/>
-      <c r="D110" s="140"/>
-      <c r="E110" s="140"/>
-      <c r="F110" s="140"/>
-      <c r="G110" s="140"/>
+      <c r="A110" s="137"/>
+      <c r="B110" s="143" t="s">
+        <v>505</v>
+      </c>
+      <c r="C110" s="138"/>
+      <c r="D110" s="138"/>
+      <c r="E110" s="138"/>
+      <c r="F110" s="138"/>
+      <c r="G110" s="138"/>
       <c r="H110" s="15"/>
       <c r="I110" s="12"/>
       <c r="J110" s="16"/>
-      <c r="K110" s="142"/>
+      <c r="K110" s="140"/>
       <c r="L110" s="16" t="s">
         <v>297</v>
       </c>
@@ -22729,19 +22815,19 @@
       <c r="AL110" s="21"/>
     </row>
     <row r="111" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="141"/>
+      <c r="A111" s="139"/>
       <c r="B111" s="128" t="s">
-        <v>512</v>
-      </c>
-      <c r="C111" s="134"/>
-      <c r="D111" s="134"/>
-      <c r="E111" s="134"/>
+        <v>508</v>
+      </c>
+      <c r="C111" s="132"/>
+      <c r="D111" s="132"/>
+      <c r="E111" s="132"/>
       <c r="F111" s="96"/>
       <c r="G111" s="96"/>
       <c r="H111" s="15"/>
       <c r="I111" s="12"/>
       <c r="J111" s="16"/>
-      <c r="K111" s="142"/>
+      <c r="K111" s="140"/>
       <c r="L111" s="16" t="s">
         <v>167</v>
       </c>
@@ -22790,7 +22876,7 @@
       <c r="I112" s="16"/>
       <c r="J112" s="16"/>
       <c r="K112" s="129" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="L112" s="129"/>
       <c r="M112" s="129"/>
@@ -22799,8 +22885,8 @@
       <c r="AC112" s="16"/>
       <c r="AD112" s="16"/>
       <c r="AE112" s="21"/>
-      <c r="AF112" s="145" t="s">
-        <v>513</v>
+      <c r="AF112" s="143" t="s">
+        <v>509</v>
       </c>
       <c r="AG112" s="16"/>
       <c r="AH112" s="16"/>
@@ -22853,7 +22939,7 @@
         <v>146</v>
       </c>
       <c r="B114" s="128" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C114" s="82"/>
       <c r="D114" s="16"/>
@@ -22863,7 +22949,7 @@
       <c r="H114" s="15"/>
       <c r="I114" s="16"/>
       <c r="J114" s="128" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="K114" s="16"/>
       <c r="L114" s="16"/>
@@ -22895,11 +22981,11 @@
       <c r="AL114" s="21"/>
     </row>
     <row r="115" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="139"/>
-      <c r="B115" s="140" t="s">
+      <c r="A115" s="137"/>
+      <c r="B115" s="138" t="s">
         <v>317</v>
       </c>
-      <c r="C115" s="140"/>
+      <c r="C115" s="138"/>
       <c r="D115" s="33"/>
       <c r="E115" s="33"/>
       <c r="F115" s="33"/>
@@ -22936,12 +23022,12 @@
       <c r="AI115" s="33"/>
       <c r="AJ115" s="33"/>
       <c r="AK115" s="33"/>
-      <c r="AL115" s="143"/>
+      <c r="AL115" s="141"/>
     </row>
     <row r="116" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="81"/>
       <c r="B116" s="82" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C116" s="82"/>
       <c r="D116" s="33"/>
@@ -22980,7 +23066,7 @@
       <c r="AI116" s="33"/>
       <c r="AJ116" s="33"/>
       <c r="AK116" s="33"/>
-      <c r="AL116" s="143"/>
+      <c r="AL116" s="141"/>
     </row>
     <row r="117" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="81"/>
@@ -22996,7 +23082,7 @@
       <c r="I117" s="16"/>
       <c r="J117" s="16"/>
       <c r="K117" s="128" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L117" s="128"/>
       <c r="M117" s="128"/>
@@ -23024,12 +23110,12 @@
       <c r="AI117" s="33"/>
       <c r="AJ117" s="33"/>
       <c r="AK117" s="33"/>
-      <c r="AL117" s="143"/>
+      <c r="AL117" s="141"/>
     </row>
     <row r="118" spans="1:46" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A118" s="81"/>
       <c r="B118" s="16" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C118" s="16"/>
       <c r="D118" s="33"/>
@@ -23037,29 +23123,29 @@
       <c r="F118" s="33"/>
       <c r="G118" s="33"/>
       <c r="H118" s="15"/>
-      <c r="I118" s="148"/>
-      <c r="J118" s="148"/>
-      <c r="K118" s="318" t="s">
+      <c r="I118" s="146"/>
+      <c r="J118" s="146"/>
+      <c r="K118" s="374" t="s">
+        <v>498</v>
+      </c>
+      <c r="L118" s="374"/>
+      <c r="M118" s="374"/>
+      <c r="N118" s="374"/>
+      <c r="O118" s="374"/>
+      <c r="P118" s="374" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q118" s="374"/>
+      <c r="R118" s="374"/>
+      <c r="S118" s="374"/>
+      <c r="T118" s="374"/>
+      <c r="U118" s="315" t="s">
         <v>501</v>
       </c>
-      <c r="L118" s="318"/>
-      <c r="M118" s="318"/>
-      <c r="N118" s="318"/>
-      <c r="O118" s="318"/>
-      <c r="P118" s="318" t="s">
-        <v>502</v>
-      </c>
-      <c r="Q118" s="318"/>
-      <c r="R118" s="318"/>
-      <c r="S118" s="318"/>
-      <c r="T118" s="318"/>
-      <c r="U118" s="311" t="s">
-        <v>504</v>
-      </c>
-      <c r="V118" s="312"/>
-      <c r="W118" s="313"/>
-      <c r="X118" s="148"/>
-      <c r="Y118" s="148"/>
+      <c r="V118" s="316"/>
+      <c r="W118" s="317"/>
+      <c r="X118" s="146"/>
+      <c r="Y118" s="146"/>
       <c r="Z118" s="16"/>
       <c r="AA118" s="16"/>
       <c r="AB118" s="16"/>
@@ -23072,12 +23158,12 @@
       <c r="AI118" s="33"/>
       <c r="AJ118" s="33"/>
       <c r="AK118" s="33"/>
-      <c r="AL118" s="143"/>
+      <c r="AL118" s="141"/>
     </row>
     <row r="119" spans="1:46" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A119" s="15"/>
       <c r="B119" s="16" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C119" s="16"/>
       <c r="D119" s="82"/>
@@ -23086,25 +23172,25 @@
       <c r="G119" s="82"/>
       <c r="H119" s="15"/>
       <c r="I119" s="16"/>
-      <c r="K119" s="319" t="s">
-        <v>479</v>
-      </c>
-      <c r="L119" s="319"/>
-      <c r="M119" s="319"/>
-      <c r="N119" s="319"/>
-      <c r="O119" s="319"/>
-      <c r="P119" s="319" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q119" s="319"/>
-      <c r="R119" s="319"/>
-      <c r="S119" s="319"/>
-      <c r="T119" s="319"/>
-      <c r="U119" s="310" t="s">
-        <v>503</v>
-      </c>
-      <c r="V119" s="310"/>
-      <c r="W119" s="310"/>
+      <c r="K119" s="375" t="s">
+        <v>476</v>
+      </c>
+      <c r="L119" s="375"/>
+      <c r="M119" s="375"/>
+      <c r="N119" s="375"/>
+      <c r="O119" s="375"/>
+      <c r="P119" s="375" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q119" s="375"/>
+      <c r="R119" s="375"/>
+      <c r="S119" s="375"/>
+      <c r="T119" s="375"/>
+      <c r="U119" s="314" t="s">
+        <v>500</v>
+      </c>
+      <c r="V119" s="314"/>
+      <c r="W119" s="314"/>
       <c r="AB119" s="16"/>
       <c r="AC119" s="16"/>
       <c r="AD119" s="16"/>
@@ -23115,39 +23201,39 @@
       <c r="AI119" s="33"/>
       <c r="AJ119" s="33"/>
       <c r="AK119" s="33"/>
-      <c r="AL119" s="143"/>
+      <c r="AL119" s="141"/>
     </row>
     <row r="120" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="15"/>
       <c r="B120" s="16" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C120" s="16"/>
-      <c r="D120" s="140"/>
-      <c r="E120" s="140"/>
-      <c r="F120" s="140"/>
-      <c r="G120" s="140"/>
+      <c r="D120" s="138"/>
+      <c r="E120" s="138"/>
+      <c r="F120" s="138"/>
+      <c r="G120" s="138"/>
       <c r="H120" s="15"/>
       <c r="I120" s="16"/>
-      <c r="K120" s="314" t="s">
-        <v>481</v>
-      </c>
-      <c r="L120" s="314"/>
-      <c r="M120" s="314"/>
-      <c r="N120" s="314"/>
-      <c r="O120" s="314"/>
-      <c r="P120" s="314" t="s">
-        <v>482</v>
-      </c>
-      <c r="Q120" s="314"/>
-      <c r="R120" s="314"/>
-      <c r="S120" s="314"/>
-      <c r="T120" s="314"/>
-      <c r="U120" s="309" t="s">
-        <v>503</v>
-      </c>
-      <c r="V120" s="309"/>
-      <c r="W120" s="309"/>
+      <c r="K120" s="309" t="s">
+        <v>478</v>
+      </c>
+      <c r="L120" s="309"/>
+      <c r="M120" s="309"/>
+      <c r="N120" s="309"/>
+      <c r="O120" s="309"/>
+      <c r="P120" s="309" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q120" s="309"/>
+      <c r="R120" s="309"/>
+      <c r="S120" s="309"/>
+      <c r="T120" s="309"/>
+      <c r="U120" s="313" t="s">
+        <v>500</v>
+      </c>
+      <c r="V120" s="313"/>
+      <c r="W120" s="313"/>
       <c r="AB120" s="16"/>
       <c r="AC120" s="16"/>
       <c r="AD120" s="16"/>
@@ -23158,12 +23244,12 @@
       <c r="AI120" s="33"/>
       <c r="AJ120" s="33"/>
       <c r="AK120" s="33"/>
-      <c r="AL120" s="143"/>
+      <c r="AL120" s="141"/>
     </row>
     <row r="121" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="15"/>
       <c r="B121" s="16" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C121" s="16"/>
       <c r="D121" s="82"/>
@@ -23172,25 +23258,25 @@
       <c r="G121" s="82"/>
       <c r="H121" s="15"/>
       <c r="I121" s="16"/>
-      <c r="K121" s="314" t="s">
-        <v>483</v>
-      </c>
-      <c r="L121" s="314"/>
-      <c r="M121" s="314"/>
-      <c r="N121" s="314"/>
-      <c r="O121" s="314"/>
-      <c r="P121" s="314" t="s">
+      <c r="K121" s="309" t="s">
+        <v>480</v>
+      </c>
+      <c r="L121" s="309"/>
+      <c r="M121" s="309"/>
+      <c r="N121" s="309"/>
+      <c r="O121" s="309"/>
+      <c r="P121" s="309" t="s">
         <v>89</v>
       </c>
-      <c r="Q121" s="314"/>
-      <c r="R121" s="314"/>
-      <c r="S121" s="314"/>
-      <c r="T121" s="314"/>
-      <c r="U121" s="309" t="s">
-        <v>503</v>
-      </c>
-      <c r="V121" s="309"/>
-      <c r="W121" s="309"/>
+      <c r="Q121" s="309"/>
+      <c r="R121" s="309"/>
+      <c r="S121" s="309"/>
+      <c r="T121" s="309"/>
+      <c r="U121" s="313" t="s">
+        <v>500</v>
+      </c>
+      <c r="V121" s="313"/>
+      <c r="W121" s="313"/>
       <c r="AB121" s="16"/>
       <c r="AC121" s="16"/>
       <c r="AD121" s="16"/>
@@ -23201,12 +23287,12 @@
       <c r="AI121" s="33"/>
       <c r="AJ121" s="33"/>
       <c r="AK121" s="33"/>
-      <c r="AL121" s="143"/>
+      <c r="AL121" s="141"/>
     </row>
     <row r="122" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="15"/>
       <c r="B122" s="16" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C122" s="16"/>
       <c r="D122" s="16"/>
@@ -23215,25 +23301,25 @@
       <c r="G122" s="16"/>
       <c r="H122" s="15"/>
       <c r="I122" s="16"/>
-      <c r="K122" s="314" t="s">
-        <v>484</v>
-      </c>
-      <c r="L122" s="314"/>
-      <c r="M122" s="314"/>
-      <c r="N122" s="314"/>
-      <c r="O122" s="314"/>
-      <c r="P122" s="314" t="s">
+      <c r="K122" s="309" t="s">
+        <v>481</v>
+      </c>
+      <c r="L122" s="309"/>
+      <c r="M122" s="309"/>
+      <c r="N122" s="309"/>
+      <c r="O122" s="309"/>
+      <c r="P122" s="309" t="s">
         <v>90</v>
       </c>
-      <c r="Q122" s="314"/>
-      <c r="R122" s="314"/>
-      <c r="S122" s="314"/>
-      <c r="T122" s="314"/>
-      <c r="U122" s="309" t="s">
-        <v>503</v>
-      </c>
-      <c r="V122" s="309"/>
-      <c r="W122" s="309"/>
+      <c r="Q122" s="309"/>
+      <c r="R122" s="309"/>
+      <c r="S122" s="309"/>
+      <c r="T122" s="309"/>
+      <c r="U122" s="313" t="s">
+        <v>500</v>
+      </c>
+      <c r="V122" s="313"/>
+      <c r="W122" s="313"/>
       <c r="AB122" s="16"/>
       <c r="AC122" s="16"/>
       <c r="AD122" s="16"/>
@@ -23244,12 +23330,12 @@
       <c r="AI122" s="33"/>
       <c r="AJ122" s="33"/>
       <c r="AK122" s="33"/>
-      <c r="AL122" s="143"/>
+      <c r="AL122" s="141"/>
     </row>
     <row r="123" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="15"/>
       <c r="B123" s="16" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C123" s="16"/>
       <c r="D123" s="16"/>
@@ -23258,25 +23344,25 @@
       <c r="G123" s="16"/>
       <c r="H123" s="15"/>
       <c r="I123" s="16"/>
-      <c r="K123" s="314" t="s">
-        <v>485</v>
-      </c>
-      <c r="L123" s="314"/>
-      <c r="M123" s="314"/>
-      <c r="N123" s="314"/>
-      <c r="O123" s="314"/>
-      <c r="P123" s="314" t="s">
+      <c r="K123" s="309" t="s">
+        <v>482</v>
+      </c>
+      <c r="L123" s="309"/>
+      <c r="M123" s="309"/>
+      <c r="N123" s="309"/>
+      <c r="O123" s="309"/>
+      <c r="P123" s="309" t="s">
         <v>91</v>
       </c>
-      <c r="Q123" s="314"/>
-      <c r="R123" s="314"/>
-      <c r="S123" s="314"/>
-      <c r="T123" s="314"/>
-      <c r="U123" s="309" t="s">
-        <v>503</v>
-      </c>
-      <c r="V123" s="309"/>
-      <c r="W123" s="309"/>
+      <c r="Q123" s="309"/>
+      <c r="R123" s="309"/>
+      <c r="S123" s="309"/>
+      <c r="T123" s="309"/>
+      <c r="U123" s="313" t="s">
+        <v>500</v>
+      </c>
+      <c r="V123" s="313"/>
+      <c r="W123" s="313"/>
       <c r="AB123" s="16"/>
       <c r="AC123" s="16"/>
       <c r="AD123" s="16"/>
@@ -23286,12 +23372,12 @@
       <c r="AI123" s="96"/>
       <c r="AJ123" s="96"/>
       <c r="AK123" s="96"/>
-      <c r="AL123" s="143"/>
+      <c r="AL123" s="141"/>
     </row>
     <row r="124" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="15"/>
       <c r="B124" s="30" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C124" s="12"/>
       <c r="D124" s="16"/>
@@ -23300,25 +23386,25 @@
       <c r="G124" s="16"/>
       <c r="H124" s="15"/>
       <c r="I124" s="16"/>
-      <c r="K124" s="314" t="s">
-        <v>486</v>
-      </c>
-      <c r="L124" s="314"/>
-      <c r="M124" s="314"/>
-      <c r="N124" s="314"/>
-      <c r="O124" s="314"/>
-      <c r="P124" s="314" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q124" s="314"/>
-      <c r="R124" s="314"/>
-      <c r="S124" s="314"/>
-      <c r="T124" s="314"/>
-      <c r="U124" s="309" t="s">
-        <v>503</v>
-      </c>
-      <c r="V124" s="309"/>
-      <c r="W124" s="309"/>
+      <c r="K124" s="309" t="s">
+        <v>483</v>
+      </c>
+      <c r="L124" s="309"/>
+      <c r="M124" s="309"/>
+      <c r="N124" s="309"/>
+      <c r="O124" s="309"/>
+      <c r="P124" s="309" t="s">
+        <v>484</v>
+      </c>
+      <c r="Q124" s="309"/>
+      <c r="R124" s="309"/>
+      <c r="S124" s="309"/>
+      <c r="T124" s="309"/>
+      <c r="U124" s="313" t="s">
+        <v>500</v>
+      </c>
+      <c r="V124" s="313"/>
+      <c r="W124" s="313"/>
       <c r="AB124" s="16"/>
       <c r="AC124" s="16"/>
       <c r="AD124" s="16"/>
@@ -23341,25 +23427,25 @@
       <c r="G125" s="16"/>
       <c r="H125" s="15"/>
       <c r="I125" s="16"/>
-      <c r="K125" s="314" t="s">
-        <v>488</v>
-      </c>
-      <c r="L125" s="314"/>
-      <c r="M125" s="314"/>
-      <c r="N125" s="314"/>
-      <c r="O125" s="314"/>
-      <c r="P125" s="314" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q125" s="314"/>
-      <c r="R125" s="314"/>
-      <c r="S125" s="314"/>
-      <c r="T125" s="314"/>
-      <c r="U125" s="309" t="s">
-        <v>503</v>
-      </c>
-      <c r="V125" s="309"/>
-      <c r="W125" s="309"/>
+      <c r="K125" s="309" t="s">
+        <v>485</v>
+      </c>
+      <c r="L125" s="309"/>
+      <c r="M125" s="309"/>
+      <c r="N125" s="309"/>
+      <c r="O125" s="309"/>
+      <c r="P125" s="309" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q125" s="309"/>
+      <c r="R125" s="309"/>
+      <c r="S125" s="309"/>
+      <c r="T125" s="309"/>
+      <c r="U125" s="313" t="s">
+        <v>500</v>
+      </c>
+      <c r="V125" s="313"/>
+      <c r="W125" s="313"/>
       <c r="AB125" s="16"/>
       <c r="AC125" s="16"/>
       <c r="AD125" s="16"/>
@@ -23370,7 +23456,7 @@
       <c r="AI125" s="33"/>
       <c r="AJ125" s="33"/>
       <c r="AK125" s="33"/>
-      <c r="AL125" s="143"/>
+      <c r="AL125" s="141"/>
     </row>
     <row r="126" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="12"/>
@@ -23382,25 +23468,25 @@
       <c r="G126" s="16"/>
       <c r="H126" s="15"/>
       <c r="I126" s="16"/>
-      <c r="K126" s="314" t="s">
-        <v>490</v>
-      </c>
-      <c r="L126" s="314"/>
-      <c r="M126" s="314"/>
-      <c r="N126" s="314"/>
-      <c r="O126" s="314"/>
-      <c r="P126" s="314" t="s">
-        <v>491</v>
-      </c>
-      <c r="Q126" s="314"/>
-      <c r="R126" s="314"/>
-      <c r="S126" s="314"/>
-      <c r="T126" s="314"/>
-      <c r="U126" s="309" t="s">
-        <v>503</v>
-      </c>
-      <c r="V126" s="309"/>
-      <c r="W126" s="309"/>
+      <c r="K126" s="309" t="s">
+        <v>487</v>
+      </c>
+      <c r="L126" s="309"/>
+      <c r="M126" s="309"/>
+      <c r="N126" s="309"/>
+      <c r="O126" s="309"/>
+      <c r="P126" s="309" t="s">
+        <v>488</v>
+      </c>
+      <c r="Q126" s="309"/>
+      <c r="R126" s="309"/>
+      <c r="S126" s="309"/>
+      <c r="T126" s="309"/>
+      <c r="U126" s="313" t="s">
+        <v>500</v>
+      </c>
+      <c r="V126" s="313"/>
+      <c r="W126" s="313"/>
       <c r="AD126" s="16"/>
       <c r="AE126" s="21"/>
       <c r="AF126" s="16"/>
@@ -23421,25 +23507,25 @@
       <c r="G127" s="16"/>
       <c r="H127" s="15"/>
       <c r="I127" s="16"/>
-      <c r="K127" s="314" t="s">
-        <v>492</v>
-      </c>
-      <c r="L127" s="314"/>
-      <c r="M127" s="314"/>
-      <c r="N127" s="314"/>
-      <c r="O127" s="314"/>
-      <c r="P127" s="314" t="s">
+      <c r="K127" s="309" t="s">
+        <v>489</v>
+      </c>
+      <c r="L127" s="309"/>
+      <c r="M127" s="309"/>
+      <c r="N127" s="309"/>
+      <c r="O127" s="309"/>
+      <c r="P127" s="309" t="s">
         <v>127</v>
       </c>
-      <c r="Q127" s="314"/>
-      <c r="R127" s="314"/>
-      <c r="S127" s="314"/>
-      <c r="T127" s="314"/>
-      <c r="U127" s="309" t="s">
-        <v>503</v>
-      </c>
-      <c r="V127" s="309"/>
-      <c r="W127" s="309"/>
+      <c r="Q127" s="309"/>
+      <c r="R127" s="309"/>
+      <c r="S127" s="309"/>
+      <c r="T127" s="309"/>
+      <c r="U127" s="313" t="s">
+        <v>500</v>
+      </c>
+      <c r="V127" s="313"/>
+      <c r="W127" s="313"/>
       <c r="AD127" s="16"/>
       <c r="AE127" s="16"/>
       <c r="AF127" s="15"/>
@@ -23460,25 +23546,25 @@
       <c r="G128" s="16"/>
       <c r="H128" s="15"/>
       <c r="I128" s="16"/>
-      <c r="K128" s="314" t="s">
-        <v>493</v>
-      </c>
-      <c r="L128" s="314"/>
-      <c r="M128" s="314"/>
-      <c r="N128" s="314"/>
-      <c r="O128" s="314"/>
-      <c r="P128" s="314" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q128" s="314"/>
-      <c r="R128" s="314"/>
-      <c r="S128" s="314"/>
-      <c r="T128" s="314"/>
-      <c r="U128" s="309">
+      <c r="K128" s="309" t="s">
+        <v>490</v>
+      </c>
+      <c r="L128" s="309"/>
+      <c r="M128" s="309"/>
+      <c r="N128" s="309"/>
+      <c r="O128" s="309"/>
+      <c r="P128" s="309" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q128" s="309"/>
+      <c r="R128" s="309"/>
+      <c r="S128" s="309"/>
+      <c r="T128" s="309"/>
+      <c r="U128" s="313">
         <v>0</v>
       </c>
-      <c r="V128" s="309"/>
-      <c r="W128" s="309"/>
+      <c r="V128" s="313"/>
+      <c r="W128" s="313"/>
       <c r="AD128" s="16"/>
       <c r="AE128" s="21"/>
       <c r="AF128" s="16"/>
@@ -23490,7 +23576,7 @@
       <c r="AL128" s="16"/>
     </row>
     <row r="129" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="144"/>
+      <c r="A129" s="142"/>
       <c r="B129" s="33"/>
       <c r="C129" s="33"/>
       <c r="D129" s="33"/>
@@ -23499,28 +23585,28 @@
       <c r="G129" s="33"/>
       <c r="H129" s="15"/>
       <c r="I129" s="16"/>
-      <c r="K129" s="314" t="s">
-        <v>495</v>
-      </c>
-      <c r="L129" s="314"/>
-      <c r="M129" s="314"/>
-      <c r="N129" s="314"/>
-      <c r="O129" s="314"/>
-      <c r="P129" s="314" t="s">
+      <c r="K129" s="309" t="s">
+        <v>492</v>
+      </c>
+      <c r="L129" s="309"/>
+      <c r="M129" s="309"/>
+      <c r="N129" s="309"/>
+      <c r="O129" s="309"/>
+      <c r="P129" s="309" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q129" s="309"/>
+      <c r="R129" s="309"/>
+      <c r="S129" s="309"/>
+      <c r="T129" s="309"/>
+      <c r="U129" s="313" t="s">
         <v>496</v>
       </c>
-      <c r="Q129" s="314"/>
-      <c r="R129" s="314"/>
-      <c r="S129" s="314"/>
-      <c r="T129" s="314"/>
-      <c r="U129" s="309" t="s">
-        <v>499</v>
-      </c>
-      <c r="V129" s="309"/>
-      <c r="W129" s="309"/>
+      <c r="V129" s="313"/>
+      <c r="W129" s="313"/>
       <c r="AD129" s="16"/>
       <c r="AE129" s="21"/>
-      <c r="AF129" s="140"/>
+      <c r="AF129" s="138"/>
       <c r="AG129" s="96"/>
       <c r="AH129" s="96"/>
       <c r="AI129" s="96"/>
@@ -23538,25 +23624,25 @@
       <c r="G130" s="16"/>
       <c r="H130" s="15"/>
       <c r="I130" s="16"/>
-      <c r="K130" s="314" t="s">
+      <c r="K130" s="309" t="s">
+        <v>494</v>
+      </c>
+      <c r="L130" s="309"/>
+      <c r="M130" s="309"/>
+      <c r="N130" s="309"/>
+      <c r="O130" s="309"/>
+      <c r="P130" s="309" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q130" s="309"/>
+      <c r="R130" s="309"/>
+      <c r="S130" s="309"/>
+      <c r="T130" s="309"/>
+      <c r="U130" s="313" t="s">
         <v>497</v>
       </c>
-      <c r="L130" s="314"/>
-      <c r="M130" s="314"/>
-      <c r="N130" s="314"/>
-      <c r="O130" s="314"/>
-      <c r="P130" s="314" t="s">
-        <v>498</v>
-      </c>
-      <c r="Q130" s="314"/>
-      <c r="R130" s="314"/>
-      <c r="S130" s="314"/>
-      <c r="T130" s="314"/>
-      <c r="U130" s="309" t="s">
-        <v>500</v>
-      </c>
-      <c r="V130" s="309"/>
-      <c r="W130" s="309"/>
+      <c r="V130" s="313"/>
+      <c r="W130" s="313"/>
       <c r="AD130" s="16"/>
       <c r="AE130" s="21"/>
       <c r="AF130" s="16"/>
@@ -23627,7 +23713,7 @@
       <c r="I133" s="16"/>
       <c r="J133" s="16"/>
       <c r="K133" s="16" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="L133" s="16"/>
       <c r="M133" s="16"/>
@@ -23712,7 +23798,7 @@
       <c r="J135" s="16"/>
       <c r="K135" s="12"/>
       <c r="L135" s="82" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="M135" s="82"/>
       <c r="N135" s="82"/>
@@ -23753,7 +23839,7 @@
       <c r="I136" s="16"/>
       <c r="J136" s="82"/>
       <c r="K136" s="128" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="L136" s="16"/>
       <c r="M136" s="16"/>
@@ -23775,8 +23861,8 @@
       <c r="AC136" s="16"/>
       <c r="AD136" s="16"/>
       <c r="AE136" s="21"/>
-      <c r="AF136" s="145" t="s">
-        <v>478</v>
+      <c r="AF136" s="143" t="s">
+        <v>475</v>
       </c>
       <c r="AG136" s="16"/>
       <c r="AH136" s="16"/>
@@ -23826,7 +23912,7 @@
       <c r="AL137" s="16"/>
     </row>
     <row r="138" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="144"/>
+      <c r="A138" s="142"/>
       <c r="B138" s="33"/>
       <c r="C138" s="33"/>
       <c r="D138" s="33"/>
@@ -23879,7 +23965,7 @@
       <c r="I139" s="16"/>
       <c r="J139" s="16"/>
       <c r="K139" s="128" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L139" s="16"/>
       <c r="M139" s="16"/>
@@ -23901,16 +23987,16 @@
       <c r="AC139" s="16"/>
       <c r="AD139" s="16"/>
       <c r="AE139" s="21"/>
-      <c r="AF139" s="145"/>
-      <c r="AG139" s="146"/>
-      <c r="AH139" s="146"/>
-      <c r="AI139" s="146"/>
-      <c r="AJ139" s="146"/>
-      <c r="AK139" s="146"/>
-      <c r="AL139" s="147"/>
+      <c r="AF139" s="143"/>
+      <c r="AG139" s="144"/>
+      <c r="AH139" s="144"/>
+      <c r="AI139" s="144"/>
+      <c r="AJ139" s="144"/>
+      <c r="AK139" s="144"/>
+      <c r="AL139" s="145"/>
     </row>
     <row r="140" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="144"/>
+      <c r="A140" s="142"/>
       <c r="B140" s="33"/>
       <c r="C140" s="33"/>
       <c r="D140" s="33"/>
@@ -23984,30 +24070,30 @@
       <c r="AL141" s="16"/>
     </row>
     <row r="142" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="367" t="s">
+      <c r="A142" s="361" t="s">
         <v>38</v>
       </c>
-      <c r="B142" s="367"/>
-      <c r="C142" s="367"/>
-      <c r="D142" s="315" t="s">
+      <c r="B142" s="361"/>
+      <c r="C142" s="361"/>
+      <c r="D142" s="310" t="s">
         <v>306</v>
       </c>
-      <c r="E142" s="316"/>
-      <c r="F142" s="317"/>
-      <c r="G142" s="367" t="s">
+      <c r="E142" s="311"/>
+      <c r="F142" s="312"/>
+      <c r="G142" s="361" t="s">
         <v>40</v>
       </c>
-      <c r="H142" s="367"/>
-      <c r="I142" s="367"/>
-      <c r="J142" s="315" t="s">
+      <c r="H142" s="361"/>
+      <c r="I142" s="361"/>
+      <c r="J142" s="310" t="s">
         <v>355</v>
       </c>
-      <c r="K142" s="316"/>
-      <c r="L142" s="316"/>
-      <c r="M142" s="316"/>
-      <c r="N142" s="316"/>
-      <c r="O142" s="316"/>
-      <c r="P142" s="317"/>
+      <c r="K142" s="311"/>
+      <c r="L142" s="311"/>
+      <c r="M142" s="311"/>
+      <c r="N142" s="311"/>
+      <c r="O142" s="311"/>
+      <c r="P142" s="312"/>
       <c r="Q142" s="101"/>
       <c r="R142" s="101"/>
       <c r="S142" s="101"/>
@@ -24032,61 +24118,61 @@
       <c r="AL142" s="102"/>
     </row>
     <row r="143" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="367" t="s">
+      <c r="A143" s="361" t="s">
         <v>130</v>
       </c>
-      <c r="B143" s="367"/>
-      <c r="C143" s="367"/>
-      <c r="D143" s="367"/>
-      <c r="E143" s="367"/>
-      <c r="F143" s="367"/>
-      <c r="G143" s="367"/>
-      <c r="H143" s="370" t="s">
+      <c r="B143" s="361"/>
+      <c r="C143" s="361"/>
+      <c r="D143" s="361"/>
+      <c r="E143" s="361"/>
+      <c r="F143" s="361"/>
+      <c r="G143" s="361"/>
+      <c r="H143" s="368" t="s">
         <v>131</v>
       </c>
-      <c r="I143" s="371"/>
-      <c r="J143" s="371"/>
-      <c r="K143" s="371"/>
-      <c r="L143" s="371"/>
-      <c r="M143" s="371"/>
-      <c r="N143" s="371"/>
-      <c r="O143" s="371"/>
-      <c r="P143" s="371"/>
-      <c r="Q143" s="371"/>
-      <c r="R143" s="371"/>
-      <c r="S143" s="371"/>
-      <c r="T143" s="371"/>
-      <c r="U143" s="371"/>
-      <c r="V143" s="371"/>
-      <c r="W143" s="371"/>
-      <c r="X143" s="371"/>
-      <c r="Y143" s="371"/>
-      <c r="Z143" s="371"/>
-      <c r="AA143" s="371"/>
-      <c r="AB143" s="371"/>
-      <c r="AC143" s="371"/>
-      <c r="AD143" s="371"/>
-      <c r="AE143" s="372"/>
-      <c r="AF143" s="367" t="s">
+      <c r="I143" s="369"/>
+      <c r="J143" s="369"/>
+      <c r="K143" s="369"/>
+      <c r="L143" s="369"/>
+      <c r="M143" s="369"/>
+      <c r="N143" s="369"/>
+      <c r="O143" s="369"/>
+      <c r="P143" s="369"/>
+      <c r="Q143" s="369"/>
+      <c r="R143" s="369"/>
+      <c r="S143" s="369"/>
+      <c r="T143" s="369"/>
+      <c r="U143" s="369"/>
+      <c r="V143" s="369"/>
+      <c r="W143" s="369"/>
+      <c r="X143" s="369"/>
+      <c r="Y143" s="369"/>
+      <c r="Z143" s="369"/>
+      <c r="AA143" s="369"/>
+      <c r="AB143" s="369"/>
+      <c r="AC143" s="369"/>
+      <c r="AD143" s="369"/>
+      <c r="AE143" s="370"/>
+      <c r="AF143" s="361" t="s">
         <v>132</v>
       </c>
-      <c r="AG143" s="367"/>
-      <c r="AH143" s="367"/>
-      <c r="AI143" s="367"/>
-      <c r="AJ143" s="367"/>
-      <c r="AK143" s="367"/>
-      <c r="AL143" s="367"/>
+      <c r="AG143" s="361"/>
+      <c r="AH143" s="361"/>
+      <c r="AI143" s="361"/>
+      <c r="AJ143" s="361"/>
+      <c r="AK143" s="361"/>
+      <c r="AL143" s="361"/>
     </row>
     <row r="144" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="373" t="s">
+      <c r="A144" s="371" t="s">
         <v>307</v>
       </c>
-      <c r="B144" s="374"/>
-      <c r="C144" s="374"/>
-      <c r="D144" s="374"/>
-      <c r="E144" s="374"/>
-      <c r="F144" s="374"/>
-      <c r="G144" s="375"/>
+      <c r="B144" s="372"/>
+      <c r="C144" s="372"/>
+      <c r="D144" s="372"/>
+      <c r="E144" s="372"/>
+      <c r="F144" s="372"/>
+      <c r="G144" s="373"/>
       <c r="H144" s="4"/>
       <c r="I144" s="5" t="s">
         <v>314</v>
@@ -24113,13 +24199,13 @@
       <c r="AC144" s="5"/>
       <c r="AD144" s="5"/>
       <c r="AE144" s="11"/>
-      <c r="AF144" s="365"/>
-      <c r="AG144" s="365"/>
-      <c r="AH144" s="365"/>
-      <c r="AI144" s="365"/>
-      <c r="AJ144" s="365"/>
-      <c r="AK144" s="365"/>
-      <c r="AL144" s="366"/>
+      <c r="AF144" s="359"/>
+      <c r="AG144" s="359"/>
+      <c r="AH144" s="359"/>
+      <c r="AI144" s="359"/>
+      <c r="AJ144" s="359"/>
+      <c r="AK144" s="359"/>
+      <c r="AL144" s="360"/>
     </row>
     <row r="145" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="5" t="s">
@@ -24157,24 +24243,24 @@
       <c r="AC145" s="1"/>
       <c r="AD145" s="1"/>
       <c r="AE145" s="107"/>
-      <c r="AF145" s="350"/>
-      <c r="AG145" s="350"/>
-      <c r="AH145" s="350"/>
-      <c r="AI145" s="350"/>
-      <c r="AJ145" s="350"/>
-      <c r="AK145" s="350"/>
-      <c r="AL145" s="351"/>
+      <c r="AF145" s="344"/>
+      <c r="AG145" s="344"/>
+      <c r="AH145" s="344"/>
+      <c r="AI145" s="344"/>
+      <c r="AJ145" s="344"/>
+      <c r="AK145" s="344"/>
+      <c r="AL145" s="345"/>
     </row>
     <row r="146" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="354" t="s">
+      <c r="A146" s="348" t="s">
         <v>290</v>
       </c>
-      <c r="B146" s="355"/>
-      <c r="C146" s="355"/>
-      <c r="D146" s="355"/>
-      <c r="E146" s="355"/>
-      <c r="F146" s="355"/>
-      <c r="G146" s="355"/>
+      <c r="B146" s="349"/>
+      <c r="C146" s="349"/>
+      <c r="D146" s="349"/>
+      <c r="E146" s="349"/>
+      <c r="F146" s="349"/>
+      <c r="G146" s="349"/>
       <c r="H146" s="104"/>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -24210,15 +24296,15 @@
       <c r="AL146" s="108"/>
     </row>
     <row r="147" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="354" t="s">
+      <c r="A147" s="348" t="s">
         <v>134</v>
       </c>
-      <c r="B147" s="355"/>
-      <c r="C147" s="355"/>
-      <c r="D147" s="355"/>
-      <c r="E147" s="355"/>
-      <c r="F147" s="355"/>
-      <c r="G147" s="355"/>
+      <c r="B147" s="349"/>
+      <c r="C147" s="349"/>
+      <c r="D147" s="349"/>
+      <c r="E147" s="349"/>
+      <c r="F147" s="349"/>
+      <c r="G147" s="349"/>
       <c r="H147" s="104"/>
       <c r="I147" s="1"/>
       <c r="J147" s="1"/>
@@ -24278,59 +24364,59 @@
       <c r="AC148" s="1"/>
       <c r="AD148" s="1"/>
       <c r="AE148" s="107"/>
-      <c r="AF148" s="355"/>
-      <c r="AG148" s="355"/>
-      <c r="AH148" s="355"/>
-      <c r="AI148" s="355"/>
-      <c r="AJ148" s="355"/>
-      <c r="AK148" s="355"/>
-      <c r="AL148" s="364"/>
+      <c r="AF148" s="349"/>
+      <c r="AG148" s="349"/>
+      <c r="AH148" s="349"/>
+      <c r="AI148" s="349"/>
+      <c r="AJ148" s="349"/>
+      <c r="AK148" s="349"/>
+      <c r="AL148" s="358"/>
     </row>
     <row r="149" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="354" t="s">
+      <c r="A149" s="348" t="s">
         <v>313</v>
       </c>
-      <c r="B149" s="355"/>
-      <c r="C149" s="355"/>
-      <c r="D149" s="355"/>
-      <c r="E149" s="355"/>
-      <c r="F149" s="355"/>
-      <c r="G149" s="355"/>
+      <c r="B149" s="349"/>
+      <c r="C149" s="349"/>
+      <c r="D149" s="349"/>
+      <c r="E149" s="349"/>
+      <c r="F149" s="349"/>
+      <c r="G149" s="349"/>
       <c r="H149" s="104"/>
       <c r="J149" s="1" t="s">
         <v>309</v>
       </c>
       <c r="AE149" s="107"/>
-      <c r="AF149" s="355" t="s">
+      <c r="AF149" s="349" t="s">
         <v>298</v>
       </c>
-      <c r="AG149" s="355"/>
-      <c r="AH149" s="355"/>
-      <c r="AI149" s="355"/>
-      <c r="AJ149" s="355"/>
-      <c r="AK149" s="355"/>
-      <c r="AL149" s="364"/>
+      <c r="AG149" s="349"/>
+      <c r="AH149" s="349"/>
+      <c r="AI149" s="349"/>
+      <c r="AJ149" s="349"/>
+      <c r="AK149" s="349"/>
+      <c r="AL149" s="358"/>
     </row>
     <row r="150" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="354"/>
-      <c r="B150" s="355"/>
-      <c r="C150" s="355"/>
-      <c r="D150" s="355"/>
-      <c r="E150" s="355"/>
-      <c r="F150" s="355"/>
-      <c r="G150" s="355"/>
+      <c r="A150" s="348"/>
+      <c r="B150" s="349"/>
+      <c r="C150" s="349"/>
+      <c r="D150" s="349"/>
+      <c r="E150" s="349"/>
+      <c r="F150" s="349"/>
+      <c r="G150" s="349"/>
       <c r="H150" s="104"/>
       <c r="K150" s="1" t="s">
         <v>310</v>
       </c>
       <c r="AE150" s="107"/>
-      <c r="AF150" s="350"/>
-      <c r="AG150" s="350"/>
-      <c r="AH150" s="350"/>
-      <c r="AI150" s="350"/>
-      <c r="AJ150" s="350"/>
-      <c r="AK150" s="350"/>
-      <c r="AL150" s="351"/>
+      <c r="AF150" s="344"/>
+      <c r="AG150" s="344"/>
+      <c r="AH150" s="344"/>
+      <c r="AI150" s="344"/>
+      <c r="AJ150" s="344"/>
+      <c r="AK150" s="344"/>
+      <c r="AL150" s="345"/>
     </row>
     <row r="151" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="68"/>
@@ -24351,15 +24437,15 @@
       <c r="AL151" s="108"/>
     </row>
     <row r="152" spans="1:38" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="355" t="s">
+      <c r="A152" s="349" t="s">
         <v>298</v>
       </c>
-      <c r="B152" s="355"/>
-      <c r="C152" s="355"/>
-      <c r="D152" s="355"/>
-      <c r="E152" s="355"/>
-      <c r="F152" s="355"/>
-      <c r="G152" s="364"/>
+      <c r="B152" s="349"/>
+      <c r="C152" s="349"/>
+      <c r="D152" s="349"/>
+      <c r="E152" s="349"/>
+      <c r="F152" s="349"/>
+      <c r="G152" s="358"/>
       <c r="H152" s="104"/>
       <c r="J152" s="1" t="s">
         <v>311</v>
@@ -24374,13 +24460,13 @@
       <c r="AL152" s="108"/>
     </row>
     <row r="153" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="354"/>
-      <c r="B153" s="355"/>
-      <c r="C153" s="355"/>
-      <c r="D153" s="355"/>
-      <c r="E153" s="355"/>
-      <c r="F153" s="355"/>
-      <c r="G153" s="355"/>
+      <c r="A153" s="348"/>
+      <c r="B153" s="349"/>
+      <c r="C153" s="349"/>
+      <c r="D153" s="349"/>
+      <c r="E153" s="349"/>
+      <c r="F153" s="349"/>
+      <c r="G153" s="349"/>
       <c r="H153" s="104"/>
       <c r="I153" s="1"/>
       <c r="J153" s="1"/>
@@ -24405,22 +24491,22 @@
       <c r="AC153" s="1"/>
       <c r="AD153" s="1"/>
       <c r="AE153" s="107"/>
-      <c r="AF153" s="350"/>
-      <c r="AG153" s="350"/>
-      <c r="AH153" s="350"/>
-      <c r="AI153" s="350"/>
-      <c r="AJ153" s="350"/>
-      <c r="AK153" s="350"/>
-      <c r="AL153" s="351"/>
+      <c r="AF153" s="344"/>
+      <c r="AG153" s="344"/>
+      <c r="AH153" s="344"/>
+      <c r="AI153" s="344"/>
+      <c r="AJ153" s="344"/>
+      <c r="AK153" s="344"/>
+      <c r="AL153" s="345"/>
     </row>
     <row r="154" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="354"/>
-      <c r="B154" s="355"/>
-      <c r="C154" s="355"/>
-      <c r="D154" s="355"/>
-      <c r="E154" s="355"/>
-      <c r="F154" s="355"/>
-      <c r="G154" s="355"/>
+      <c r="A154" s="348"/>
+      <c r="B154" s="349"/>
+      <c r="C154" s="349"/>
+      <c r="D154" s="349"/>
+      <c r="E154" s="349"/>
+      <c r="F154" s="349"/>
+      <c r="G154" s="349"/>
       <c r="H154" s="104"/>
       <c r="I154" s="1"/>
       <c r="J154" s="1" t="s">
@@ -24447,13 +24533,13 @@
       <c r="AC154" s="1"/>
       <c r="AD154" s="1"/>
       <c r="AE154" s="107"/>
-      <c r="AF154" s="350"/>
-      <c r="AG154" s="350"/>
-      <c r="AH154" s="350"/>
-      <c r="AI154" s="350"/>
-      <c r="AJ154" s="350"/>
-      <c r="AK154" s="350"/>
-      <c r="AL154" s="351"/>
+      <c r="AF154" s="344"/>
+      <c r="AG154" s="344"/>
+      <c r="AH154" s="344"/>
+      <c r="AI154" s="344"/>
+      <c r="AJ154" s="344"/>
+      <c r="AK154" s="344"/>
+      <c r="AL154" s="345"/>
     </row>
     <row r="155" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="103"/>
@@ -24540,13 +24626,13 @@
       <c r="AL156" s="108"/>
     </row>
     <row r="157" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="355"/>
-      <c r="B157" s="355"/>
-      <c r="C157" s="355"/>
-      <c r="D157" s="355"/>
-      <c r="E157" s="355"/>
-      <c r="F157" s="355"/>
-      <c r="G157" s="364"/>
+      <c r="A157" s="349"/>
+      <c r="B157" s="349"/>
+      <c r="C157" s="349"/>
+      <c r="D157" s="349"/>
+      <c r="E157" s="349"/>
+      <c r="F157" s="349"/>
+      <c r="G157" s="358"/>
       <c r="H157" s="104"/>
       <c r="I157" s="1"/>
       <c r="J157" s="5"/>
@@ -24620,15 +24706,15 @@
       <c r="AL158" s="108"/>
     </row>
     <row r="159" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="354" t="s">
+      <c r="A159" s="348" t="s">
         <v>384</v>
       </c>
-      <c r="B159" s="355"/>
-      <c r="C159" s="355"/>
-      <c r="D159" s="355"/>
-      <c r="E159" s="355"/>
-      <c r="F159" s="355"/>
-      <c r="G159" s="364"/>
+      <c r="B159" s="349"/>
+      <c r="C159" s="349"/>
+      <c r="D159" s="349"/>
+      <c r="E159" s="349"/>
+      <c r="F159" s="349"/>
+      <c r="G159" s="358"/>
       <c r="H159" s="4"/>
       <c r="I159" s="5" t="s">
         <v>315</v>
@@ -24708,15 +24794,15 @@
       <c r="AL160" s="108"/>
     </row>
     <row r="161" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="354" t="s">
+      <c r="A161" s="348" t="s">
         <v>146</v>
       </c>
-      <c r="B161" s="355"/>
-      <c r="C161" s="355"/>
-      <c r="D161" s="355"/>
-      <c r="E161" s="355"/>
-      <c r="F161" s="355"/>
-      <c r="G161" s="364"/>
+      <c r="B161" s="349"/>
+      <c r="C161" s="349"/>
+      <c r="D161" s="349"/>
+      <c r="E161" s="349"/>
+      <c r="F161" s="349"/>
+      <c r="G161" s="358"/>
       <c r="H161" s="4"/>
       <c r="I161" s="5"/>
       <c r="J161" s="100"/>
@@ -24829,13 +24915,13 @@
       <c r="AC163" s="1"/>
       <c r="AD163" s="1"/>
       <c r="AE163" s="107"/>
-      <c r="AF163" s="350"/>
-      <c r="AG163" s="350"/>
-      <c r="AH163" s="350"/>
-      <c r="AI163" s="350"/>
-      <c r="AJ163" s="350"/>
-      <c r="AK163" s="350"/>
-      <c r="AL163" s="351"/>
+      <c r="AF163" s="344"/>
+      <c r="AG163" s="344"/>
+      <c r="AH163" s="344"/>
+      <c r="AI163" s="344"/>
+      <c r="AJ163" s="344"/>
+      <c r="AK163" s="344"/>
+      <c r="AL163" s="345"/>
     </row>
     <row r="164" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="H164" s="104"/>
@@ -26213,15 +26299,15 @@
       <c r="AL196" s="5"/>
     </row>
     <row r="197" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="354" t="s">
+      <c r="A197" s="348" t="s">
         <v>384</v>
       </c>
-      <c r="B197" s="355"/>
-      <c r="C197" s="355"/>
-      <c r="D197" s="355"/>
-      <c r="E197" s="355"/>
-      <c r="F197" s="355"/>
-      <c r="G197" s="364"/>
+      <c r="B197" s="349"/>
+      <c r="C197" s="349"/>
+      <c r="D197" s="349"/>
+      <c r="E197" s="349"/>
+      <c r="F197" s="349"/>
+      <c r="G197" s="358"/>
       <c r="H197" s="4"/>
       <c r="I197" s="5" t="s">
         <v>327</v>
@@ -26292,24 +26378,24 @@
       <c r="AC198" s="1"/>
       <c r="AD198" s="1"/>
       <c r="AE198" s="107"/>
-      <c r="AF198" s="350"/>
-      <c r="AG198" s="350"/>
-      <c r="AH198" s="350"/>
-      <c r="AI198" s="350"/>
-      <c r="AJ198" s="350"/>
-      <c r="AK198" s="350"/>
-      <c r="AL198" s="351"/>
+      <c r="AF198" s="344"/>
+      <c r="AG198" s="344"/>
+      <c r="AH198" s="344"/>
+      <c r="AI198" s="344"/>
+      <c r="AJ198" s="344"/>
+      <c r="AK198" s="344"/>
+      <c r="AL198" s="345"/>
     </row>
     <row r="199" spans="1:38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="354" t="s">
+      <c r="A199" s="348" t="s">
         <v>146</v>
       </c>
-      <c r="B199" s="355"/>
-      <c r="C199" s="355"/>
-      <c r="D199" s="355"/>
-      <c r="E199" s="355"/>
-      <c r="F199" s="355"/>
-      <c r="G199" s="364"/>
+      <c r="B199" s="349"/>
+      <c r="C199" s="349"/>
+      <c r="D199" s="349"/>
+      <c r="E199" s="349"/>
+      <c r="F199" s="349"/>
+      <c r="G199" s="358"/>
       <c r="H199" s="4"/>
       <c r="I199" s="5"/>
       <c r="J199" s="100"/>
@@ -27316,15 +27402,23 @@
     </row>
   </sheetData>
   <mergeCells count="194">
-    <mergeCell ref="A143:G143"/>
-    <mergeCell ref="H143:AE143"/>
-    <mergeCell ref="AF143:AL143"/>
-    <mergeCell ref="A144:G144"/>
-    <mergeCell ref="AF144:AL144"/>
-    <mergeCell ref="A146:G146"/>
-    <mergeCell ref="A107:G107"/>
-    <mergeCell ref="A197:G197"/>
     <mergeCell ref="AF198:AL198"/>
+    <mergeCell ref="AF145:AL145"/>
+    <mergeCell ref="A147:G147"/>
+    <mergeCell ref="A108:G108"/>
+    <mergeCell ref="K123:O123"/>
+    <mergeCell ref="P123:T123"/>
+    <mergeCell ref="K124:O124"/>
+    <mergeCell ref="P124:T124"/>
+    <mergeCell ref="K125:O125"/>
+    <mergeCell ref="P125:T125"/>
+    <mergeCell ref="K126:O126"/>
+    <mergeCell ref="P126:T126"/>
+    <mergeCell ref="K118:O118"/>
+    <mergeCell ref="P118:T118"/>
+    <mergeCell ref="K119:O119"/>
+    <mergeCell ref="P119:T119"/>
+    <mergeCell ref="AF91:AL91"/>
     <mergeCell ref="A199:G199"/>
     <mergeCell ref="A149:G149"/>
     <mergeCell ref="AF148:AL148"/>
@@ -27340,11 +27434,14 @@
     <mergeCell ref="A150:G150"/>
     <mergeCell ref="AF150:AL150"/>
     <mergeCell ref="A152:G152"/>
-    <mergeCell ref="AF145:AL145"/>
-    <mergeCell ref="A147:G147"/>
-    <mergeCell ref="AF90:AL90"/>
-    <mergeCell ref="A92:G92"/>
-    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="A143:G143"/>
+    <mergeCell ref="H143:AE143"/>
+    <mergeCell ref="AF143:AL143"/>
+    <mergeCell ref="A144:G144"/>
+    <mergeCell ref="AF144:AL144"/>
+    <mergeCell ref="A146:G146"/>
+    <mergeCell ref="A107:G107"/>
+    <mergeCell ref="A197:G197"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="D142:F142"/>
     <mergeCell ref="G142:I142"/>
@@ -27355,15 +27452,11 @@
     <mergeCell ref="A90:G90"/>
     <mergeCell ref="H90:AE90"/>
     <mergeCell ref="A97:G97"/>
-    <mergeCell ref="AF97:AL97"/>
-    <mergeCell ref="AF92:AL92"/>
     <mergeCell ref="A98:G98"/>
-    <mergeCell ref="AF98:AL98"/>
     <mergeCell ref="A100:G100"/>
     <mergeCell ref="A95:G95"/>
-    <mergeCell ref="AF95:AL95"/>
     <mergeCell ref="A96:G96"/>
-    <mergeCell ref="AF96:AL96"/>
+    <mergeCell ref="A91:G91"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
@@ -27431,6 +27524,8 @@
     <mergeCell ref="P44:Z44"/>
     <mergeCell ref="AA44:AD44"/>
     <mergeCell ref="AF14:AL14"/>
+    <mergeCell ref="P52:Z52"/>
+    <mergeCell ref="A103:G103"/>
     <mergeCell ref="AF20:AL20"/>
     <mergeCell ref="AA52:AD52"/>
     <mergeCell ref="K47:O47"/>
@@ -27445,9 +27540,18 @@
     <mergeCell ref="K46:O46"/>
     <mergeCell ref="P46:Z46"/>
     <mergeCell ref="AA46:AD46"/>
-    <mergeCell ref="A91:G91"/>
-    <mergeCell ref="AF91:AL91"/>
-    <mergeCell ref="A108:G108"/>
+    <mergeCell ref="AF90:AL90"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="AF97:AL97"/>
+    <mergeCell ref="AF92:AL92"/>
+    <mergeCell ref="AF98:AL98"/>
+    <mergeCell ref="AF95:AL95"/>
+    <mergeCell ref="AF96:AL96"/>
+    <mergeCell ref="K127:O127"/>
+    <mergeCell ref="P127:T127"/>
+    <mergeCell ref="K128:O128"/>
+    <mergeCell ref="P128:T128"/>
     <mergeCell ref="AF106:AL106"/>
     <mergeCell ref="A102:G102"/>
     <mergeCell ref="AL1:AL2"/>
@@ -27468,30 +27572,6 @@
     <mergeCell ref="P51:Z51"/>
     <mergeCell ref="AA51:AD51"/>
     <mergeCell ref="K52:O52"/>
-    <mergeCell ref="P52:Z52"/>
-    <mergeCell ref="K123:O123"/>
-    <mergeCell ref="P123:T123"/>
-    <mergeCell ref="K124:O124"/>
-    <mergeCell ref="P124:T124"/>
-    <mergeCell ref="K125:O125"/>
-    <mergeCell ref="P125:T125"/>
-    <mergeCell ref="K126:O126"/>
-    <mergeCell ref="P126:T126"/>
-    <mergeCell ref="A103:G103"/>
-    <mergeCell ref="K118:O118"/>
-    <mergeCell ref="P118:T118"/>
-    <mergeCell ref="K119:O119"/>
-    <mergeCell ref="P119:T119"/>
-    <mergeCell ref="K120:O120"/>
-    <mergeCell ref="P120:T120"/>
-    <mergeCell ref="K121:O121"/>
-    <mergeCell ref="P121:T121"/>
-    <mergeCell ref="K122:O122"/>
-    <mergeCell ref="P122:T122"/>
-    <mergeCell ref="K127:O127"/>
-    <mergeCell ref="P127:T127"/>
-    <mergeCell ref="K128:O128"/>
-    <mergeCell ref="P128:T128"/>
     <mergeCell ref="K129:O129"/>
     <mergeCell ref="P129:T129"/>
     <mergeCell ref="K130:O130"/>
@@ -27510,6 +27590,12 @@
     <mergeCell ref="U124:W124"/>
     <mergeCell ref="U123:W123"/>
     <mergeCell ref="U122:W122"/>
+    <mergeCell ref="K120:O120"/>
+    <mergeCell ref="P120:T120"/>
+    <mergeCell ref="K121:O121"/>
+    <mergeCell ref="P121:T121"/>
+    <mergeCell ref="K122:O122"/>
+    <mergeCell ref="P122:T122"/>
   </mergeCells>
   <phoneticPr fontId="22"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27523,617 +27609,673 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultColWidth="3.77734375" defaultRowHeight="16.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" style="128"/>
-    <col min="2" max="2" width="15.21875" style="128" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="128" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36" style="128" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" style="16"/>
+    <col min="2" max="2" width="15.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="3.77734375" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="16" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B2" s="131" t="s">
+      <c r="B2" s="147" t="s">
         <v>401</v>
       </c>
-      <c r="C2" s="131" t="s">
+      <c r="C2" s="147" t="s">
         <v>399</v>
       </c>
-      <c r="D2" s="131" t="s">
+      <c r="D2" s="147" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C3" s="133" t="s">
+      <c r="C3" s="148" t="s">
         <v>404</v>
       </c>
-      <c r="D3" s="132" t="s">
+      <c r="D3" s="63" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C4" s="132" t="s">
+      <c r="C4" s="63" t="s">
         <v>402</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C5" s="132" t="s">
+      <c r="C5" s="63" t="s">
         <v>403</v>
       </c>
-      <c r="D5" s="132" t="s">
+      <c r="D5" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B6" s="132" t="s">
+      <c r="B6" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C6" s="132" t="s">
+      <c r="C6" s="63" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="132" t="s">
+      <c r="D6" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B7" s="132" t="s">
+      <c r="B7" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C7" s="132" t="s">
+      <c r="C7" s="63" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="132" t="s">
+      <c r="D7" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C8" s="132" t="s">
+      <c r="C8" s="63" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="132" t="s">
+      <c r="D8" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B9" s="132" t="s">
+      <c r="B9" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C9" s="132" t="s">
+      <c r="C9" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="132" t="s">
+      <c r="D9" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B10" s="132" t="s">
+      <c r="B10" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C10" s="132" t="s">
+      <c r="C10" s="63" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="132" t="s">
+      <c r="D10" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B11" s="132" t="s">
+      <c r="B11" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C11" s="132" t="s">
+      <c r="C11" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="D11" s="132" t="s">
+      <c r="D11" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="63" t="s">
         <v>263</v>
       </c>
-      <c r="C12" s="132" t="s">
+      <c r="C12" s="63" t="s">
         <v>161</v>
       </c>
-      <c r="D12" s="132" t="s">
+      <c r="D12" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B13" s="132" t="s">
-        <v>263</v>
-      </c>
-      <c r="C13" s="132" t="s">
+      <c r="B13" s="63" t="s">
+        <v>512</v>
+      </c>
+      <c r="C13" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="132" t="s">
+      <c r="D13" s="63" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B14" s="132" t="s">
+      <c r="B14" s="131" t="s">
+        <v>513</v>
+      </c>
+      <c r="C14" s="131" t="s">
+        <v>520</v>
+      </c>
+      <c r="D14" s="131" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B15" s="63" t="s">
+        <v>464</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>408</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B16" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>430</v>
+      </c>
+      <c r="D16" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B17" s="63" t="s">
+        <v>514</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>407</v>
+      </c>
+      <c r="D17" s="63" t="s">
         <v>467</v>
       </c>
-      <c r="C14" s="132" t="s">
-        <v>408</v>
-      </c>
-      <c r="D14" s="132" t="s">
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B18" s="131" t="s">
+        <v>514</v>
+      </c>
+      <c r="C18" s="131" t="s">
+        <v>522</v>
+      </c>
+      <c r="D18" s="131" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B19" s="63" t="s">
+        <v>427</v>
+      </c>
+      <c r="C19" s="148" t="s">
+        <v>426</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B20" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C20" s="63" t="s">
+        <v>402</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B21" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C21" s="63" t="s">
+        <v>403</v>
+      </c>
+      <c r="D21" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B22" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C22" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="D22" s="63" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B23" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C23" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B24" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C24" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B25" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C25" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B26" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C26" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B27" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B28" s="63" t="s">
+        <v>425</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B29" s="63" t="s">
+        <v>515</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B30" s="131" t="s">
+        <v>516</v>
+      </c>
+      <c r="C30" s="131" t="s">
+        <v>521</v>
+      </c>
+      <c r="D30" s="131" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B31" s="63" t="s">
+        <v>466</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>404</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B32" s="63" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B15" s="132" t="s">
-        <v>265</v>
-      </c>
-      <c r="C15" s="132" t="s">
-        <v>430</v>
-      </c>
-      <c r="D15" s="132" t="s">
+      <c r="C32" s="148" t="s">
+        <v>432</v>
+      </c>
+      <c r="D32" s="63" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B33" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C33" s="63" t="s">
+        <v>402</v>
+      </c>
+      <c r="D33" s="63" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B16" s="132" t="s">
-        <v>265</v>
-      </c>
-      <c r="C16" s="132" t="s">
-        <v>407</v>
-      </c>
-      <c r="D16" s="132" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B17" s="132" t="s">
-        <v>427</v>
-      </c>
-      <c r="C17" s="133" t="s">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B34" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C34" s="63" t="s">
+        <v>403</v>
+      </c>
+      <c r="D34" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B35" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C35" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" s="63" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B36" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B37" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C37" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B38" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C38" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B39" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C39" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B40" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C40" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B41" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C41" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B42" s="63" t="s">
+        <v>517</v>
+      </c>
+      <c r="C42" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="D42" s="63" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B43" s="131" t="s">
+        <v>518</v>
+      </c>
+      <c r="C43" s="131" t="s">
+        <v>522</v>
+      </c>
+      <c r="D43" s="131" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B44" s="63" t="s">
+        <v>519</v>
+      </c>
+      <c r="C44" s="63" t="s">
+        <v>434</v>
+      </c>
+      <c r="D44" s="63" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B45" s="131" t="s">
+        <v>519</v>
+      </c>
+      <c r="C45" s="131" t="s">
+        <v>523</v>
+      </c>
+      <c r="D45" s="131" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B46" s="63" t="s">
+        <v>529</v>
+      </c>
+      <c r="C46" s="148" t="s">
+        <v>429</v>
+      </c>
+      <c r="D46" s="63" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B47" s="63" t="s">
+        <v>437</v>
+      </c>
+      <c r="C47" s="63" t="s">
+        <v>435</v>
+      </c>
+      <c r="D47" s="63" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B48" s="63" t="s">
+        <v>324</v>
+      </c>
+      <c r="C48" s="148" t="s">
+        <v>429</v>
+      </c>
+      <c r="D48" s="63" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B49" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C49" s="63" t="s">
+        <v>435</v>
+      </c>
+      <c r="D49" s="63" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B50" s="63" t="s">
+        <v>440</v>
+      </c>
+      <c r="C50" s="148" t="s">
         <v>426</v>
       </c>
-      <c r="D17" s="132" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B18" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C18" s="132" t="s">
+      <c r="D50" s="63" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B51" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="63" t="s">
         <v>402</v>
       </c>
-      <c r="D18" s="132" t="s">
+      <c r="D51" s="63" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B19" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C19" s="132" t="s">
+    <row r="52" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B52" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="63" t="s">
         <v>403</v>
       </c>
-      <c r="D19" s="132" t="s">
+      <c r="D52" s="63" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B20" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C20" s="132" t="s">
+    <row r="53" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B53" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="63" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="132" t="s">
+      <c r="D53" s="63" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B21" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C21" s="132" t="s">
+    <row r="54" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B54" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="63" t="s">
         <v>157</v>
       </c>
-      <c r="D21" s="132" t="s">
+      <c r="D54" s="63" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B22" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C22" s="132" t="s">
+    <row r="55" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B55" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" s="63" t="s">
         <v>158</v>
       </c>
-      <c r="D22" s="132" t="s">
+      <c r="D55" s="63" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B23" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C23" s="132" t="s">
+    <row r="56" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B56" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="132" t="s">
+      <c r="D56" s="63" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B24" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C24" s="132" t="s">
+    <row r="57" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B57" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="63" t="s">
         <v>159</v>
       </c>
-      <c r="D24" s="132" t="s">
+      <c r="D57" s="63" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B25" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C25" s="132" t="s">
+    <row r="58" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B58" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="D25" s="132" t="s">
+      <c r="D58" s="63" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B26" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C26" s="132" t="s">
+    <row r="59" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B59" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" s="63" t="s">
         <v>161</v>
       </c>
-      <c r="D26" s="132" t="s">
+      <c r="D59" s="63" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B27" s="132" t="s">
-        <v>425</v>
-      </c>
-      <c r="C27" s="132" t="s">
+    <row r="60" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B60" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="D27" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B28" s="132" t="s">
-        <v>469</v>
-      </c>
-      <c r="C28" s="132" t="s">
-        <v>404</v>
-      </c>
-      <c r="D28" s="132" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B29" s="132" t="s">
-        <v>471</v>
-      </c>
-      <c r="C29" s="133" t="s">
-        <v>432</v>
-      </c>
-      <c r="D29" s="132" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B30" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C30" s="132" t="s">
-        <v>402</v>
-      </c>
-      <c r="D30" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B31" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C31" s="132" t="s">
-        <v>403</v>
-      </c>
-      <c r="D31" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B32" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C32" s="132" t="s">
-        <v>156</v>
-      </c>
-      <c r="D32" s="132" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B33" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C33" s="132" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B34" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C34" s="132" t="s">
-        <v>158</v>
-      </c>
-      <c r="D34" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B35" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C35" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B36" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C36" s="132" t="s">
-        <v>159</v>
-      </c>
-      <c r="D36" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B37" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C37" s="132" t="s">
-        <v>160</v>
-      </c>
-      <c r="D37" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B38" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C38" s="132" t="s">
-        <v>161</v>
-      </c>
-      <c r="D38" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B39" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="C39" s="132" t="s">
-        <v>162</v>
-      </c>
-      <c r="D39" s="132" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B40" s="132" t="s">
-        <v>272</v>
-      </c>
-      <c r="C40" s="132" t="s">
-        <v>434</v>
-      </c>
-      <c r="D40" s="132" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B41" s="132" t="s">
-        <v>439</v>
-      </c>
-      <c r="C41" s="133" t="s">
-        <v>429</v>
-      </c>
-      <c r="D41" s="132" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B42" s="132" t="s">
-        <v>437</v>
-      </c>
-      <c r="C42" s="132" t="s">
-        <v>435</v>
-      </c>
-      <c r="D42" s="132" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B43" s="132" t="s">
-        <v>438</v>
-      </c>
-      <c r="C43" s="133" t="s">
-        <v>429</v>
-      </c>
-      <c r="D43" s="132" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B44" s="132" t="s">
-        <v>441</v>
-      </c>
-      <c r="C44" s="132" t="s">
-        <v>435</v>
-      </c>
-      <c r="D44" s="132" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B45" s="132" t="s">
-        <v>443</v>
-      </c>
-      <c r="C45" s="133" t="s">
-        <v>426</v>
-      </c>
-      <c r="D45" s="132" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B46" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C46" s="132" t="s">
-        <v>402</v>
-      </c>
-      <c r="D46" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B47" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C47" s="132" t="s">
-        <v>403</v>
-      </c>
-      <c r="D47" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B48" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="132" t="s">
-        <v>156</v>
-      </c>
-      <c r="D48" s="132" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B49" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" s="132" t="s">
-        <v>157</v>
-      </c>
-      <c r="D49" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B50" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C50" s="132" t="s">
-        <v>158</v>
-      </c>
-      <c r="D50" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B51" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C51" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="D51" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B52" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" s="132" t="s">
-        <v>159</v>
-      </c>
-      <c r="D52" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B53" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C53" s="132" t="s">
-        <v>160</v>
-      </c>
-      <c r="D53" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B54" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C54" s="132" t="s">
-        <v>161</v>
-      </c>
-      <c r="D54" s="132" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B55" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="C55" s="132" t="s">
-        <v>162</v>
-      </c>
-      <c r="D55" s="132" t="s">
+      <c r="D60" s="63" t="s">
         <v>433</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="22"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>